--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/reiProjects/product-automation/govgrants-product-automation/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0281DBE3-15CB-4490-BC3C-E53F70F6C052}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9255EE-873C-C841-80D4-D2DAF798101E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="4720" yWindow="7720" windowWidth="23260" windowHeight="12580" firstSheet="2" activeTab="9" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement" sheetId="1" r:id="rId1"/>
@@ -594,14 +594,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -623,7 +623,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -634,7 +634,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -654,13 +654,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -682,7 +682,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -693,7 +693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -704,7 +704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -712,10 +712,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -726,7 +726,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -737,7 +737,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -748,7 +748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -759,7 +759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -770,7 +770,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -781,7 +781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -792,7 +792,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -803,7 +803,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -823,13 +823,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -840,7 +840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -851,7 +851,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -862,7 +862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -873,7 +873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -884,7 +884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -895,7 +895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -906,7 +906,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -917,7 +917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -928,7 +928,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -939,7 +939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -950,7 +950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -961,7 +961,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -972,7 +972,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -991,13 +991,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1159,13 +1159,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1207,13 +1207,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1375,14 +1375,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1536,14 +1536,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1705,14 +1705,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1765,12 +1765,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1822,14 +1822,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1881,14 +1881,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1941,14 +1941,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2091,13 +2091,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2240,14 +2240,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2288,13 +2288,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/reiProjects/product-automation/govgrants-product-automation/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9255EE-873C-C841-80D4-D2DAF798101E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97439E79-019C-4B47-ACA6-145966278B85}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4720" yWindow="7720" windowWidth="23260" windowHeight="12580" firstSheet="2" activeTab="9" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="9" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement" sheetId="1" r:id="rId1"/>
@@ -216,14 +216,14 @@
     <t>Automation  Announcement1</t>
   </si>
   <si>
-    <t>Automation Competitive Announcement</t>
+    <t>Automation Competitive Announcement </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +246,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,7 +261,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -263,12 +269,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -278,6 +299,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -594,14 +618,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -612,7 +636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -623,7 +647,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -634,7 +658,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -654,13 +678,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,7 +695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -682,7 +706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -693,7 +717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -704,7 +728,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -715,7 +739,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -726,7 +750,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -737,7 +761,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -748,7 +772,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -759,7 +783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -770,7 +794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -781,7 +805,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -792,7 +816,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -803,7 +827,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -823,13 +847,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -840,7 +864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -851,7 +875,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -862,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -873,7 +897,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -884,7 +908,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -895,7 +919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -906,7 +930,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -917,7 +941,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -928,7 +952,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -939,7 +963,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -950,7 +974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -961,7 +985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -972,7 +996,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -991,13 +1015,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1019,7 +1043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1030,7 +1054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1041,7 +1065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1052,7 +1076,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1063,7 +1087,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1074,7 +1098,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1085,7 +1109,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1096,7 +1120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1107,7 +1131,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1118,7 +1142,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1129,7 +1153,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1140,7 +1164,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1159,13 +1183,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1187,7 +1211,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1207,13 +1231,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1235,7 +1259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1246,7 +1270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1257,7 +1281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1268,7 +1292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1279,7 +1303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1290,7 +1314,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1301,7 +1325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1312,7 +1336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1323,7 +1347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1334,7 +1358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1345,7 +1369,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1356,7 +1380,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1375,14 +1399,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1393,7 +1417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1415,7 +1439,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1426,7 +1450,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1437,7 +1461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1505,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1492,7 +1516,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1503,7 +1527,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1514,7 +1538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1536,14 +1560,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1565,7 +1589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1576,7 +1600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1587,7 +1611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1598,7 +1622,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1609,7 +1633,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1620,7 +1644,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1631,7 +1655,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1642,7 +1666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1699,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1710,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1705,14 +1729,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1723,18 +1747,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1745,7 +1769,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1765,12 +1789,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1792,7 +1816,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1803,7 +1827,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1822,14 +1846,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1840,7 +1864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1851,7 +1875,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1862,7 +1886,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1881,14 +1905,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,7 +1923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1910,7 +1934,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1921,7 +1945,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1941,14 +1965,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1959,7 +1983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1981,7 +2005,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1992,7 +2016,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2003,7 +2027,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2014,7 +2038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2025,7 +2049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2060,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2047,7 +2071,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2058,7 +2082,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2069,7 +2093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2091,13 +2115,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2108,7 +2132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2119,7 +2143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2130,7 +2154,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2141,7 +2165,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2152,7 +2176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2163,7 +2187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2174,7 +2198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2185,7 +2209,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2196,7 +2220,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2207,7 +2231,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2218,7 +2242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2240,14 +2264,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2269,7 +2293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2288,13 +2312,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2305,7 +2329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2316,7 +2340,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2327,7 +2351,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2362,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2349,7 +2373,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45333E3-697A-4E2F-86DC-2EA558FA1E0F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5CA9D9-5112-485B-B073-07E31699D469}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4097" yWindow="1029" windowWidth="16457" windowHeight="8554" firstSheet="6" activeTab="7" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -121,15 +121,6 @@
     <t>GranteeMatch__c</t>
   </si>
   <si>
-    <t>QSubmissionDeadline__c</t>
-  </si>
-  <si>
-    <t>AResponseDeadline__c</t>
-  </si>
-  <si>
-    <t>QAContactEmailAddress__c</t>
-  </si>
-  <si>
     <t>AwardFloor__c</t>
   </si>
   <si>
@@ -248,13 +239,94 @@
   </si>
   <si>
     <t>Automation Runtime Competitive Past Announcement</t>
+  </si>
+  <si>
+    <t>fieldAnnouncementName__c</t>
+  </si>
+  <si>
+    <t>fieldProgram__c</t>
+  </si>
+  <si>
+    <t>fieldBudget_Category_Package__c</t>
+  </si>
+  <si>
+    <t>fieldIsMatchRequired__c</t>
+  </si>
+  <si>
+    <t>fieldLaverageAllowed__c</t>
+  </si>
+  <si>
+    <t>fieldIsProgramIncomeAnticipated__c</t>
+  </si>
+  <si>
+    <t>fieldPreApplicationNeeded__c</t>
+  </si>
+  <si>
+    <t>fieldFocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>fieldKPIsRequired__c</t>
+  </si>
+  <si>
+    <t>fieldWBSRequired__c</t>
+  </si>
+  <si>
+    <t>fieldRiskAssessment_Required__c</t>
+  </si>
+  <si>
+    <t>fieldAreExpensesBuildIUpLevel__c</t>
+  </si>
+  <si>
+    <t>fieldIsAdvancePermitted__c</t>
+  </si>
+  <si>
+    <t>fieldIsNegotiationsAllowed__c</t>
+  </si>
+  <si>
+    <t>fieldGranteeMatch__c</t>
+  </si>
+  <si>
+    <t>fieldIsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>fieldAnnouncementDescription__c</t>
+  </si>
+  <si>
+    <t>fieldEligibleApplicantTypes__c</t>
+  </si>
+  <si>
+    <t>fieldApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>fieldQAAvailability__c</t>
+  </si>
+  <si>
+    <t>fieldQSubmissionDeadline__c</t>
+  </si>
+  <si>
+    <t>fieldAResponseDeadline__c</t>
+  </si>
+  <si>
+    <t>fieldQAContactEmailAddress__c</t>
+  </si>
+  <si>
+    <t>fieldAwardFloor__c</t>
+  </si>
+  <si>
+    <t>fieldAwardCeiling__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>fieldTotalCommittedAmount__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +356,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -306,7 +384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -319,6 +397,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -635,14 +714,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" customWidth="1"/>
-    <col min="3" max="3" width="43.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -653,40 +732,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="5"/>
     </row>
   </sheetData>
@@ -698,14 +777,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -716,128 +795,128 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C10">
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C12">
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G13">
         <v>0</v>
       </c>
@@ -853,14 +932,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -871,7 +950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -882,7 +961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -890,10 +969,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -904,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -912,21 +991,21 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -937,18 +1016,18 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -967,13 +1046,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -984,7 +1063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -995,7 +1074,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1003,10 +1082,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1017,29 +1096,29 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1047,21 +1126,21 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1072,18 +1151,18 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1103,13 +1182,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1131,7 +1210,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1139,10 +1218,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1153,29 +1232,29 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1183,21 +1262,21 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1208,18 +1287,18 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1238,14 +1317,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1256,23 +1335,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>379</v>
@@ -1286,13 +1365,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1303,59 +1382,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1367,13 +1446,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1384,147 +1463,147 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
+      <c r="B2" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
+      <c r="B3" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
+      <c r="B4" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
+      <c r="B5" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
+      <c r="B6" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
-        <v>39</v>
+      <c r="B7" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" t="s">
-        <v>37</v>
+      <c r="B8" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
-        <v>41</v>
+      <c r="B9" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B11" t="s">
-        <v>43</v>
+      <c r="B11" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
-        <v>40</v>
+      <c r="B12" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
-        <v>44</v>
+      <c r="B13" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" t="s">
-        <v>45</v>
+      <c r="B14" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1536,13 +1615,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1561,10 +1640,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1572,10 +1651,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1583,10 +1662,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1594,95 +1673,95 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1693,13 +1772,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1710,7 +1789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1721,7 +1800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1732,7 +1811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1743,7 +1822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1754,7 +1833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1762,95 +1841,95 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1861,13 +1940,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1878,7 +1957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1889,7 +1968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1900,7 +1979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1911,7 +1990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1922,7 +2001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1933,92 +2012,92 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2029,14 +2108,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.4609375" customWidth="1"/>
-    <col min="2" max="2" width="26.3046875" customWidth="1"/>
-    <col min="3" max="3" width="62.23046875" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2047,7 +2126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2055,10 +2134,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2066,10 +2145,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2077,7 +2156,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2088,14 +2167,14 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.53515625" customWidth="1"/>
-    <col min="2" max="2" width="31.69140625" customWidth="1"/>
-    <col min="3" max="3" width="14.07421875" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2106,7 +2185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2117,7 +2196,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2128,7 +2207,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2139,7 +2218,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2150,92 +2229,92 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2246,14 +2325,14 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.53515625" customWidth="1"/>
-    <col min="2" max="2" width="24.4609375" customWidth="1"/>
-    <col min="3" max="3" width="15.69140625" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2264,7 +2343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2275,7 +2354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2286,7 +2365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2297,7 +2376,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2308,7 +2387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2319,92 +2398,92 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2415,13 +2494,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2432,7 +2511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2443,7 +2522,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2454,7 +2533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2465,7 +2544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2476,7 +2555,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2487,92 +2566,92 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2583,13 +2662,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2600,26 +2679,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
         <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2631,13 +2710,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.4609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2648,7 +2727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2659,7 +2738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2670,7 +2749,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2681,7 +2760,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2692,7 +2771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2703,92 +2782,92 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2799,14 +2878,14 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2817,18 +2896,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" s="3"/>
     </row>
   </sheetData>
@@ -2839,14 +2918,14 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" customWidth="1"/>
-    <col min="3" max="3" width="43.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2857,7 +2936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2868,7 +2947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2879,7 +2958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2890,7 +2969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2901,7 +2980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2909,95 +2988,95 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3008,14 +3087,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" customWidth="1"/>
-    <col min="3" max="3" width="59.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3026,40 +3105,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
+      <c r="B4" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" s="5"/>
     </row>
   </sheetData>
@@ -3071,14 +3150,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.84375" customWidth="1"/>
-    <col min="2" max="2" width="30.07421875" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3089,7 +3168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3097,10 +3176,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3108,10 +3187,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3130,13 +3209,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.4609375" customWidth="1"/>
-    <col min="3" max="3" width="65.84375" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="65.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3147,7 +3226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3155,10 +3234,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3166,10 +3245,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3189,13 +3268,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.3046875" customWidth="1"/>
-    <col min="3" max="3" width="46.53515625" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3206,7 +3285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3214,10 +3293,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3225,10 +3304,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3247,13 +3326,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="44.69140625" customWidth="1"/>
-    <col min="3" max="3" width="38.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3264,7 +3343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3272,10 +3351,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3283,10 +3362,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3306,14 +3385,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" customWidth="1"/>
-    <col min="3" max="3" width="43.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3324,34 +3403,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -3366,14 +3445,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.3046875" customWidth="1"/>
-    <col min="3" max="3" width="43.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3384,7 +3463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3392,10 +3471,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3403,10 +3482,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5CA9D9-5112-485B-B073-07E31699D469}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA99C194-925D-4A2D-9E1F-8ED92169490D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="13" activeTab="16" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement" sheetId="1" r:id="rId1"/>
@@ -29,16 +29,17 @@
     <sheet name="BudgetPeriod" sheetId="3" r:id="rId14"/>
     <sheet name="Reviewer" sheetId="4" r:id="rId15"/>
     <sheet name="Creation Second Modal" sheetId="6" r:id="rId16"/>
-    <sheet name="Creation Second Modal for App" sheetId="25" r:id="rId17"/>
-    <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId18"/>
-    <sheet name="Creation Second Modal1" sheetId="14" r:id="rId19"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId20"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId21"/>
-    <sheet name="Creation of Second Modal" sheetId="15" r:id="rId22"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId23"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId24"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId25"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId26"/>
+    <sheet name="Competitive Creation Modal" sheetId="29" r:id="rId17"/>
+    <sheet name="Creation Second Modal for App" sheetId="25" r:id="rId18"/>
+    <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId19"/>
+    <sheet name="Creation Second Modal1" sheetId="14" r:id="rId20"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId21"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId22"/>
+    <sheet name="Creation of Second Modal" sheetId="15" r:id="rId23"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId24"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId25"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId26"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId27"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1445,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
@@ -1606,6 +1607,13 @@
         <v>33</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="6"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1613,6 +1621,197 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F19099-5305-442F-9CD7-4437184F40A1}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1769,7 +1968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1875,174 +2074,6 @@
       </c>
       <c r="C9" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2165,6 +2196,174 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2322,7 +2521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2491,7 +2690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2659,7 +2858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2707,7 +2906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2875,7 +3074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2915,7 +3114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB8BF19-4EE2-4D39-B907-89BA8F1901C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516E7C07-1B36-4E90-B9BD-F1B7CB9BAEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="28" activeTab="30" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="17" activeTab="18" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="84">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -309,6 +309,27 @@
   </si>
   <si>
     <t>For-profit organizations;Individuals</t>
+  </si>
+  <si>
+    <t>Allocationlevel__c</t>
+  </si>
+  <si>
+    <t>ApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>QAAvailability__c</t>
+  </si>
+  <si>
+    <t>QSubmissionDeadline__c</t>
+  </si>
+  <si>
+    <t>AResponseDeadline__c</t>
+  </si>
+  <si>
+    <t>QAContactEmailAddress__c</t>
+  </si>
+  <si>
+    <t>TotalCommittedAmount__c</t>
   </si>
 </sst>
 </file>
@@ -1380,8 +1401,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>54</v>
+      <c r="B4" t="s">
+        <v>78</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -1391,8 +1412,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>56</v>
+      <c r="B5" t="s">
+        <v>79</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>17</v>
@@ -1402,8 +1423,8 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>55</v>
+      <c r="B6" t="s">
+        <v>80</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1413,8 +1434,8 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>57</v>
+      <c r="B7" t="s">
+        <v>81</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1424,8 +1445,8 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>58</v>
+      <c r="B8" t="s">
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
@@ -1435,8 +1456,8 @@
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>61</v>
+      <c r="B9" t="s">
+        <v>83</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -2682,8 +2703,8 @@
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
+      <c r="B14" t="s">
+        <v>77</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>71</v>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516E7C07-1B36-4E90-B9BD-F1B7CB9BAEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE797F7-3113-44BF-93BB-AB9E927C200A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="17" activeTab="18" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="795" firstSheet="29" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -336,7 +336,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +390,12 @@
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -412,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -434,6 +440,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -751,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -815,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -879,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.81640625" customWidth="1"/>
+    <col min="1" max="1" width="33.77734375" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -939,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="65.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -999,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
-    <col min="3" max="3" width="46.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+    <col min="3" max="3" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1058,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.7265625" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1118,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1176,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
-    <col min="3" max="3" width="59.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1235,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1296,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1357,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1475,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.453125" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
-    <col min="3" max="3" width="62.1796875" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" customWidth="1"/>
+    <col min="3" max="3" width="62.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1535,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1692,9 +1699,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1807,10 +1814,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1944,10 +1951,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2080,11 +2087,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2129,10 +2136,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2211,11 +2218,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2381,10 +2388,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2550,10 +2557,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2720,11 +2727,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2891,11 +2898,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2956,9 +2963,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3109,8 +3116,8 @@
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
+      <c r="B14" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>72</v>
@@ -3125,10 +3132,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3294,9 +3301,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3463,9 +3470,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3632,9 +3639,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3800,10 +3807,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3958,10 +3965,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" customWidth="1"/>
-    <col min="2" max="2" width="31.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4117,11 +4124,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="24.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4287,9 +4294,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4455,10 +4462,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4493,9 +4500,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4663,10 +4670,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4712,9 +4719,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4881,9 +4888,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4922,10 +4929,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5092,9 +5099,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5249,10 +5256,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5313,11 +5320,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.1796875" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5373,10 +5380,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5432,10 +5439,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE797F7-3113-44BF-93BB-AB9E927C200A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD1B1F8-44D7-4E9F-BBAA-4C4D0946748F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="795" firstSheet="29" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="795" firstSheet="18" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="87">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -330,6 +330,15 @@
   </si>
   <si>
     <t>TotalCommittedAmount__c</t>
+  </si>
+  <si>
+    <t>AwardFloor__c</t>
+  </si>
+  <si>
+    <t>AwardCeiling__c</t>
+  </si>
+  <si>
+    <t>EstimatedNumberOfAwards__c</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -1576,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>76</v>
@@ -1587,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -1598,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1609,7 +1618,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1620,7 +1629,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1631,7 +1640,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
@@ -1642,7 +1651,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -1653,7 +1662,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -1664,7 +1673,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1675,7 +1684,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C12">
         <v>10000</v>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BackWardCompatibility_Project\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB8BF19-4EE2-4D39-B907-89BA8F1901C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283D775A-A01C-40E6-9AE2-C39015CBD063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="28" activeTab="30" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" activeTab="30" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD1B1F8-44D7-4E9F-BBAA-4C4D0946748F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108AF760-7F32-453A-BC3B-995134000E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="795" firstSheet="18" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="18" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="88">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>EstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>Individuals</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1553,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -1588,7 +1591,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1596,10 +1599,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1607,10 +1610,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
+        <v>78</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1618,10 +1621,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1629,10 +1632,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1640,21 +1643,21 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>81</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9">
-        <v>1000</v>
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1662,10 +1665,10 @@
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1673,10 +1676,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1684,20 +1687,31 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="G13">
+    <row r="14" spans="1:7">
+      <c r="G14">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" xr:uid="{F4D31CA5-8F43-42CF-8982-056FC1AEE3F1}"/>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{F4D31CA5-8F43-42CF-8982-056FC1AEE3F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108AF760-7F32-453A-BC3B-995134000E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28BCC2-012B-4408-A427-46FF38B8DBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="18" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="18" activeTab="18" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -472,9 +472,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -512,7 +512,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -618,7 +618,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -760,7 +760,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -770,10 +770,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -834,10 +834,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -898,9 +898,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.77734375" customWidth="1"/>
+    <col min="1" max="1" width="33.81640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -958,10 +958,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="65.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="65.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1018,10 +1018,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.21875" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.1796875" customWidth="1"/>
+    <col min="3" max="3" width="46.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1077,9 +1077,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.77734375" customWidth="1"/>
+    <col min="2" max="2" width="44.81640625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1137,10 +1137,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1195,10 +1195,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.21875" customWidth="1"/>
-    <col min="3" max="3" width="59.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1254,10 +1254,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1315,10 +1315,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1376,11 +1376,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1494,11 +1494,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" customWidth="1"/>
-    <col min="3" max="3" width="62.21875" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="62.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1554,9 +1554,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1722,9 +1722,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1837,10 +1837,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1974,10 +1974,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2110,11 +2110,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2159,10 +2159,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2241,11 +2241,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2411,10 +2411,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2580,10 +2580,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2750,11 +2750,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2905,7 +2905,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>69</v>
@@ -2921,11 +2921,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.77734375" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2986,9 +2986,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3155,10 +3155,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3324,9 +3324,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3493,9 +3493,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3662,9 +3662,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3830,10 +3830,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3988,10 +3988,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4147,11 +4147,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4317,9 +4317,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4485,10 +4485,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4523,9 +4523,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4693,10 +4693,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4742,9 +4742,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4911,9 +4911,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4952,10 +4952,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5122,9 +5122,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5279,10 +5279,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5343,11 +5343,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.21875" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5403,10 +5403,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5462,10 +5462,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28BCC2-012B-4408-A427-46FF38B8DBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFAC3B1-52AB-44FE-A624-380392BCEB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="18" activeTab="18" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="14" activeTab="16" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -472,9 +472,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -512,7 +512,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -618,7 +618,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -760,7 +760,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2565,7 +2565,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>71</v>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28BCC2-012B-4408-A427-46FF38B8DBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F493542F-8758-4938-916A-B806E683C3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="18" activeTab="18" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="27" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>Individuals</t>
+  </si>
+  <si>
+    <t>PreApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>MaxApplicationsAllowed__c</t>
   </si>
 </sst>
 </file>
@@ -472,9 +478,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -512,7 +518,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -618,7 +624,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -760,7 +766,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -770,10 +776,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -834,10 +840,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -898,9 +904,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.81640625" customWidth="1"/>
+    <col min="1" max="1" width="33.77734375" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -958,10 +964,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="65.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1018,10 +1024,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.1796875" customWidth="1"/>
-    <col min="3" max="3" width="46.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+    <col min="3" max="3" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1077,9 +1083,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.81640625" customWidth="1"/>
+    <col min="2" max="2" width="44.77734375" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1137,10 +1143,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1195,10 +1201,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
-    <col min="3" max="3" width="59.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1254,10 +1260,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1315,10 +1321,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1376,11 +1382,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1494,11 +1500,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.453125" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" customWidth="1"/>
-    <col min="3" max="3" width="62.1796875" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" customWidth="1"/>
+    <col min="3" max="3" width="62.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1554,9 +1560,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1722,9 +1728,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1836,11 +1842,11 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1873,18 +1879,18 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4">
-        <v>45</v>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1892,10 +1898,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1903,10 +1909,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1914,21 +1920,21 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
+        <v>89</v>
+      </c>
+      <c r="C7">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8">
-        <v>1000</v>
+        <v>79</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1936,10 +1942,10 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="C9">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1947,10 +1953,10 @@
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1958,9 +1964,20 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12">
         <v>100000</v>
       </c>
     </row>
@@ -1974,10 +1991,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2110,11 +2127,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2159,10 +2176,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2241,11 +2258,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2411,10 +2428,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2580,10 +2597,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2750,11 +2767,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2921,11 +2938,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2986,9 +3003,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3008,10 +3025,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3019,10 +3036,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3155,10 +3172,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3324,9 +3341,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3493,9 +3510,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3662,9 +3679,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3684,10 +3701,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3695,10 +3712,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3706,7 +3723,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -3717,7 +3734,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -3816,7 +3833,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>72</v>
@@ -3830,10 +3847,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3988,10 +4005,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4147,11 +4164,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="24.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4317,9 +4334,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4485,10 +4502,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4523,9 +4540,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4693,10 +4710,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4742,9 +4759,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4911,9 +4928,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4952,10 +4969,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5122,9 +5139,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5279,10 +5296,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5343,11 +5360,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.1796875" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5403,10 +5420,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5462,10 +5479,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F493542F-8758-4938-916A-B806E683C3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B579A1C4-F7AC-432C-8D76-BDA312F8E81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="27" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19755" windowHeight="11760" tabRatio="795" firstSheet="38" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="84">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -245,18 +245,9 @@
     <t>fieldApplicationDueDate__c</t>
   </si>
   <si>
-    <t>fieldQSubmissionDeadline__c</t>
-  </si>
-  <si>
     <t>fieldQAAvailability__c</t>
   </si>
   <si>
-    <t>fieldAResponseDeadline__c</t>
-  </si>
-  <si>
-    <t>fieldQAContactEmailAddress__c</t>
-  </si>
-  <si>
     <t>fieldAwardFloor__c</t>
   </si>
   <si>
@@ -281,18 +272,9 @@
     <t>Automation Runtime Competitive Announcement for Bulk</t>
   </si>
   <si>
-    <t>fieldAnnouncementDescription__c</t>
-  </si>
-  <si>
-    <t>fieldEligibleApplicantTypes__c</t>
-  </si>
-  <si>
     <t>By Applicant and Focus Area</t>
   </si>
   <si>
-    <t>fieldAllocationlevel__c</t>
-  </si>
-  <si>
     <t>By Applicant</t>
   </si>
   <si>
@@ -302,9 +284,6 @@
     <t>Automation Permanent Internal Program_NoFA</t>
   </si>
   <si>
-    <t>fieldDetailedBudgetingRequired__c</t>
-  </si>
-  <si>
     <t>For-profit organizations</t>
   </si>
   <si>
@@ -348,6 +327,9 @@
   </si>
   <si>
     <t>MaxApplicationsAllowed__c</t>
+  </si>
+  <si>
+    <t>DetailedBudgetingRequired__c</t>
   </si>
 </sst>
 </file>
@@ -478,9 +460,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -518,7 +500,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -624,7 +606,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -766,7 +748,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -776,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -813,7 +795,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -840,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -904,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.77734375" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -964,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="65.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="65.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1024,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.21875" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1083,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="44.77734375" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1143,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1179,7 +1161,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1201,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.21875" customWidth="1"/>
-    <col min="3" max="3" width="59.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1237,7 +1219,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1260,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1321,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1382,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1419,7 +1401,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1427,7 +1409,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -1438,7 +1420,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>17</v>
@@ -1449,7 +1431,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1460,7 +1442,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1471,7 +1453,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
@@ -1482,7 +1464,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -1500,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" customWidth="1"/>
-    <col min="3" max="3" width="62.21875" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1537,7 +1519,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1560,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1597,7 +1579,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1608,7 +1590,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1616,7 +1598,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>45</v>
@@ -1627,7 +1609,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -1638,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1649,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1660,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>46</v>
@@ -1671,7 +1653,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>1000</v>
@@ -1682,7 +1664,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>10000</v>
@@ -1693,7 +1675,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1704,7 +1686,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C13">
         <v>10000</v>
@@ -1728,9 +1710,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1765,7 +1747,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1784,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -1795,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1806,7 +1788,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>10000</v>
@@ -1817,7 +1799,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1828,7 +1810,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -1843,10 +1825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1879,7 +1861,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1890,7 +1872,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1898,7 +1880,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>45</v>
@@ -1909,7 +1891,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C6">
         <v>35</v>
@@ -1920,7 +1902,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1931,7 +1913,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -1942,7 +1924,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -1953,7 +1935,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -1964,7 +1946,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1975,7 +1957,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C12">
         <v>100000</v>
@@ -1991,10 +1973,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2027,7 +2009,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2035,7 +2017,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -2057,7 +2039,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2068,7 +2050,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -2079,7 +2061,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>1000</v>
@@ -2090,7 +2072,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -2101,7 +2083,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2112,7 +2094,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <v>100000</v>
@@ -2127,11 +2109,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2176,10 +2158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2258,11 +2240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2416,7 +2398,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2428,10 +2410,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2585,7 +2567,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2597,10 +2579,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2751,10 +2733,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2767,11 +2749,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2922,10 +2904,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2938,11 +2920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.77734375" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2975,7 +2957,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3003,9 +2985,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3157,10 +3139,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3172,10 +3154,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3329,7 +3311,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3341,9 +3323,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3498,7 +3480,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3510,9 +3492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3667,7 +3649,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3679,9 +3661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3833,10 +3815,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -3847,10 +3829,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3993,7 +3975,7 @@
         <v>70</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4005,10 +3987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4152,7 +4134,7 @@
         <v>70</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4164,11 +4146,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4322,7 +4304,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4334,9 +4316,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4491,7 +4473,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4502,10 +4484,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4525,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -4540,9 +4522,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4697,7 +4679,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4710,10 +4692,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4759,9 +4741,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4916,7 +4898,7 @@
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4928,9 +4910,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4969,10 +4951,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5139,10 +5121,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5162,7 +5144,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -5173,10 +5155,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5184,7 +5166,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -5195,7 +5177,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -5206,7 +5188,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -5217,7 +5199,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -5228,7 +5210,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>46</v>
@@ -5239,7 +5221,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -5250,7 +5232,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -5261,7 +5243,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -5272,7 +5254,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C12">
         <v>10000</v>
@@ -5296,10 +5278,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5360,11 +5342,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.21875" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5420,10 +5402,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5456,7 +5438,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5479,10 +5461,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5504,7 +5486,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F493542F-8758-4938-916A-B806E683C3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C7CDBF-3FDD-400E-A2D9-BBDD47C2EA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="27" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="27" activeTab="27" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -2619,10 +2619,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2630,10 +2630,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B579A1C4-F7AC-432C-8D76-BDA312F8E81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2D8CE3-CA29-466F-99F5-633C7D93A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19755" windowHeight="11760" tabRatio="795" firstSheet="38" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19755" windowHeight="11760" tabRatio="795" firstSheet="30" activeTab="33" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="84">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -3986,7 +3986,7 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4021,7 +4021,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -4032,7 +4032,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -4043,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -4054,7 +4054,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -4065,7 +4065,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -4076,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -4098,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4109,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -4120,7 +4120,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -4130,10 +4130,21 @@
       <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>65</v>
       </c>
     </row>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2D8CE3-CA29-466F-99F5-633C7D93A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817DBBDD-AF66-4BE3-B3CC-95CE1CD3EB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19755" windowHeight="11760" tabRatio="795" firstSheet="30" activeTab="33" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="37" activeTab="42" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -460,9 +460,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -500,7 +500,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -606,7 +606,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -748,7 +748,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -758,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.7265625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="65.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="3" max="3" width="46.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.7265625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="59.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="3" max="3" width="62.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1542,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,9 +1710,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +1973,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2109,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2263,10 +2263,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2274,10 +2274,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2410,10 +2410,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2432,10 +2432,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2443,10 +2443,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2579,10 +2579,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2601,10 +2601,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2612,10 +2612,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2749,11 +2749,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2772,10 +2772,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2783,10 +2783,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2920,11 +2920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +2985,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3154,10 +3154,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3176,10 +3176,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3187,10 +3187,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3323,9 +3323,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3345,10 +3345,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3356,10 +3356,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3492,9 +3492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3514,10 +3514,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3525,10 +3525,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3661,9 +3661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3829,10 +3829,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +3987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4157,11 +4157,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4180,10 +4180,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4191,10 +4191,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4327,9 +4327,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4349,10 +4349,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4360,10 +4360,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4495,10 +4495,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4533,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4555,10 +4555,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4566,10 +4566,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4703,10 +4703,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4752,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4774,10 +4774,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4785,10 +4785,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4921,9 +4921,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +4962,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4985,10 +4985,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4996,10 +4996,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5132,9 +5132,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5289,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5353,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5413,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5472,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2D8CE3-CA29-466F-99F5-633C7D93A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C5EEDC-D0D4-455D-BBC2-1972723B552A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19755" windowHeight="11760" tabRatio="795" firstSheet="30" activeTab="33" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19755" windowHeight="11760" tabRatio="795" firstSheet="1" activeTab="3" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817DBBDD-AF66-4BE3-B3CC-95CE1CD3EB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8840F943-9552-4D17-B462-AFC8F66380F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="37" activeTab="42" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="14" activeTab="14" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -460,9 +460,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -500,7 +500,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -606,7 +606,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -748,7 +748,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8840F943-9552-4D17-B462-AFC8F66380F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2968ECF9-4CB4-4CBD-A50D-2520E2EAB3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="14" activeTab="14" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" tabRatio="795" firstSheet="15" activeTab="20" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -758,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.7265625" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="65.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="65.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
-    <col min="3" max="3" width="46.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="44.7265625" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.26953125" customWidth="1"/>
-    <col min="3" max="3" width="59.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.453125" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
-    <col min="3" max="3" width="62.26953125" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1542,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,9 +1710,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +1973,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2109,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2410,10 +2410,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2579,10 +2579,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2749,11 +2749,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2920,11 +2920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7265625" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +2985,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3154,10 +3154,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3323,9 +3323,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3492,9 +3492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3661,9 +3661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3829,10 +3829,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +3987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" customWidth="1"/>
-    <col min="2" max="2" width="31.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4157,11 +4157,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="24.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4327,9 +4327,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4495,10 +4495,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4533,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4703,10 +4703,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4752,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4921,9 +4921,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +4962,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5132,9 +5132,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5289,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5353,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.453125" customWidth="1"/>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.26953125" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5413,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5472,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2968ECF9-4CB4-4CBD-A50D-2520E2EAB3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB986768-EEC8-4579-9001-144D172E4C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" tabRatio="795" firstSheet="15" activeTab="20" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
@@ -1755,7 +1755,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1766,7 +1766,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -1777,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1788,7 +1788,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <v>10000</v>
@@ -1799,7 +1799,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1810,7 +1810,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>10000</v>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,60 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49799022-98E7-4E20-AE7A-2D0B093D8E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB8BF19-4EE2-4D39-B907-89BA8F1901C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="0" windowWidth="20355" windowHeight="10920" firstSheet="9" activeTab="12" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="28" activeTab="30" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
-    <sheet name="DirectedAnnouncement" sheetId="1" r:id="rId1"/>
-    <sheet name="DirectedAnnouncement1" sheetId="26" r:id="rId2"/>
-    <sheet name="competitive_Ann_AdminUser" sheetId="30" r:id="rId3"/>
-    <sheet name="CompetitiveAnnBulkData" sheetId="32" r:id="rId4"/>
-    <sheet name="CompetitiveAnnouncement" sheetId="5" r:id="rId5"/>
-    <sheet name="CompAnnAppSubmitForGrantor" sheetId="28" r:id="rId6"/>
-    <sheet name="CompetitiveAnnouncementforApp" sheetId="23" r:id="rId7"/>
-    <sheet name="CompetitivePastAnnouncement" sheetId="22" r:id="rId8"/>
-    <sheet name="CompetitiveAnnouncement1" sheetId="16" r:id="rId9"/>
-    <sheet name="FormulaAnnouncement" sheetId="8" r:id="rId10"/>
-    <sheet name="Creation" sheetId="7" r:id="rId11"/>
-    <sheet name="Formula_Edition" sheetId="31" r:id="rId12"/>
-    <sheet name="Edition" sheetId="2" r:id="rId13"/>
-    <sheet name="AppDueDate" sheetId="20" r:id="rId14"/>
-    <sheet name="Edition1" sheetId="10" r:id="rId15"/>
-    <sheet name="PreAppDueDate" sheetId="21" r:id="rId16"/>
-    <sheet name="BudgetPeriod" sheetId="3" r:id="rId17"/>
-    <sheet name="Reviewer" sheetId="4" r:id="rId18"/>
-    <sheet name="Creation Second Negotiation" sheetId="29" r:id="rId19"/>
-    <sheet name="Creation Second Modal" sheetId="6" r:id="rId20"/>
-    <sheet name="Creation Second Modal for App" sheetId="25" r:id="rId21"/>
-    <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId22"/>
-    <sheet name="Creation Second Modal1" sheetId="14" r:id="rId23"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId24"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId25"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId26"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId27"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId28"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId29"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId30"/>
+    <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
+    <sheet name="DirectedAnnouncementForAdmin" sheetId="41" r:id="rId2"/>
+    <sheet name="FormulaAnn_ProgWithNoFA" sheetId="39" r:id="rId3"/>
+    <sheet name="Creation Second Modal_Directed" sheetId="38" r:id="rId4"/>
+    <sheet name="Directed_Edition" sheetId="43" r:id="rId5"/>
+    <sheet name="DirectedAnnouncement" sheetId="1" r:id="rId6"/>
+    <sheet name="DirectedAnnouncement1" sheetId="26" r:id="rId7"/>
+    <sheet name="competitive_Ann_AdminUser" sheetId="30" r:id="rId8"/>
+    <sheet name="CompetitiveAnnBulkData" sheetId="32" r:id="rId9"/>
+    <sheet name="CompetitiveAnnouncement" sheetId="5" r:id="rId10"/>
+    <sheet name="CompAnnAppSubmitForGrantor" sheetId="28" r:id="rId11"/>
+    <sheet name="CompetitiveAnnouncementforApp" sheetId="23" r:id="rId12"/>
+    <sheet name="CompetitivePastAnnouncement" sheetId="22" r:id="rId13"/>
+    <sheet name="CompetitiveAnnouncement1" sheetId="16" r:id="rId14"/>
+    <sheet name="FormulaAnn_AdminUser" sheetId="34" r:id="rId15"/>
+    <sheet name="FormulaAnn_AdminUser2" sheetId="46" r:id="rId16"/>
+    <sheet name="FormulaAnnouncement" sheetId="8" r:id="rId17"/>
+    <sheet name="Creation" sheetId="7" r:id="rId18"/>
+    <sheet name="Formula_Edition" sheetId="31" r:id="rId19"/>
+    <sheet name="Edition" sheetId="2" r:id="rId20"/>
+    <sheet name="AppDueDate" sheetId="20" r:id="rId21"/>
+    <sheet name="Edition1" sheetId="10" r:id="rId22"/>
+    <sheet name="PreAppDueDate" sheetId="21" r:id="rId23"/>
+    <sheet name="BudgetPeriod" sheetId="3" r:id="rId24"/>
+    <sheet name="Reviewer" sheetId="4" r:id="rId25"/>
+    <sheet name="Creation Second Negotiation" sheetId="29" r:id="rId26"/>
+    <sheet name="CreationFormula_ByApp_focusNo" sheetId="37" r:id="rId27"/>
+    <sheet name="Creation_Formula_ByApplicant" sheetId="35" r:id="rId28"/>
+    <sheet name="Creation_Formula_ByApp_FocusYes" sheetId="33" r:id="rId29"/>
+    <sheet name="Creation Second Modal" sheetId="6" r:id="rId30"/>
+    <sheet name="Creation_Adv_Yes" sheetId="48" r:id="rId31"/>
+    <sheet name="Creation Second Modal for App" sheetId="25" r:id="rId32"/>
+    <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId33"/>
+    <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId35"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId36"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId37"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId38"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId39"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId40"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId41"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId42"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId43"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="77">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -143,9 +167,6 @@
     <t>RiskAssessment_Required__c</t>
   </si>
   <si>
-    <t>State governments;Independent school districts</t>
-  </si>
-  <si>
     <t>WBSRequired__c</t>
   </si>
   <si>
@@ -266,14 +287,35 @@
     <t>fieldEligibleApplicantTypes__c</t>
   </si>
   <si>
-    <t>State governments;Individuals</t>
+    <t>By Applicant and Focus Area</t>
+  </si>
+  <si>
+    <t>fieldAllocationlevel__c</t>
+  </si>
+  <si>
+    <t>By Applicant</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program_NoFA</t>
+  </si>
+  <si>
+    <t>fieldDetailedBudgetingRequired__c</t>
+  </si>
+  <si>
+    <t>For-profit organizations</t>
+  </si>
+  <si>
+    <t>For-profit organizations;Individuals</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +351,24 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -331,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -345,6 +405,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -659,16 +727,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
+  <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -679,7 +748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -687,21 +756,21 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -712,7 +781,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="C12" s="5"/>
     </row>
   </sheetData>
@@ -722,16 +791,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
+  <sheetPr codeName="Sheet9"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,7 +812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -753,7 +823,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -761,10 +831,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -772,8 +842,11 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="C9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -782,16 +855,17 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.81640625" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,18 +876,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -821,10 +895,69 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
+  <sheetPr codeName="Sheet11"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="65.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -841,17 +974,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
+  <sheetPr codeName="Sheet12"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="3" max="3" width="46.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,7 +995,366 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
+  <sheetPr codeName="Sheet13"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="44.7265625" customWidth="1"/>
+    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
+  <sheetPr codeName="Sheet14"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
+  <sheetPr codeName="Sheet15"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
+  <sheetPr codeName="Sheet16"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
+  <sheetPr codeName="Sheet17"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -873,78 +1365,78 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -958,17 +1450,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="3" max="3" width="62.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
+  <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -979,152 +1532,153 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="G13">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" xr:uid="{E81D0B52-59DF-468B-AEC9-C98BD1BE50E9}"/>
+    <hyperlink ref="C8" r:id="rId1" xr:uid="{F4D31CA5-8F43-42CF-8982-056FC1AEE3F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
+  <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1135,7 +1689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1146,7 +1700,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1154,70 +1708,70 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -1228,16 +1782,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
+  <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1248,7 +1803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1259,7 +1814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1267,92 +1822,92 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>100000</v>
@@ -1364,16 +1919,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
+  <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1384,7 +1940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +1951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1403,92 +1959,92 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>100000</v>
@@ -1499,17 +2055,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
+  <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +2077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1531,7 +2088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1547,16 +2104,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
+  <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1567,7 +2125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1578,7 +2136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1589,7 +2147,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1600,23 +2158,23 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -1628,17 +2186,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr codeName="Sheet24"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1649,7 +2208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1660,7 +2219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1671,7 +2230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1682,7 +2241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1693,7 +2252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1704,7 +2263,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1715,70 +2274,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1786,17 +2356,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
+  <sheetPr codeName="Sheet25"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.140625" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1807,37 +2377,147 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1845,16 +2525,423 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
+  <sheetPr codeName="Sheet26"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
+  <sheetPr codeName="Sheet27"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr codeName="Sheet28"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1865,7 +2952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1876,7 +2963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1887,7 +2974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1898,7 +2985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1909,7 +2996,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1920,7 +3007,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1928,73 +3015,84 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2003,16 +3101,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2023,7 +3121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2031,117 +3129,139 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2149,16 +3269,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
+  <sheetPr codeName="Sheet29"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2169,7 +3290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2180,7 +3301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2191,7 +3312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2199,10 +3320,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2210,10 +3331,10 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2224,7 +3345,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2232,73 +3353,84 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2306,16 +3438,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
+  <sheetPr codeName="Sheet30"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2326,7 +3459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2337,7 +3470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2348,7 +3481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2359,7 +3492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2370,7 +3503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2378,10 +3511,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2392,70 +3525,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2463,17 +3607,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
+  <sheetPr codeName="Sheet31"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2484,7 +3628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2495,114 +3639,136 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2610,17 +3776,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2631,7 +3796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2639,65 +3804,65 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2708,7 +3873,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2716,32 +3881,32 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2752,15 +3917,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
+      <c r="B13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2768,16 +3933,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
+  <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2788,7 +3955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2799,62 +3966,62 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2865,7 +4032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2876,29 +4043,29 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2909,15 +4076,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
+      <c r="B13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2925,16 +4092,563 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
+  <sheetPr codeName="Sheet33"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
+  <sheetPr codeName="Sheet34"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
+  <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2945,26 +4659,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2973,16 +4687,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr codeName="Sheet36"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2993,7 +4708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3004,7 +4719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3015,7 +4730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3026,7 +4741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3037,7 +4752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3048,7 +4763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3059,70 +4774,81 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3130,17 +4856,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
+  <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3151,18 +4878,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:3">
       <c r="C9" s="3"/>
     </row>
   </sheetData>
@@ -3170,75 +4897,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
+  <sheetPr codeName="Sheet38"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3249,7 +4919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3260,7 +4930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3271,7 +4941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3282,7 +4952,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3293,7 +4963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3304,18 +4974,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3326,128 +4996,70 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
       <c r="C14" t="s">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3456,16 +5068,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3476,18 +5089,175 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C8" r:id="rId1" xr:uid="{06AD44E0-AFBC-4014-935E-17B00BD5175A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3495,10 +5265,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3509,8 +5279,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C9" s="5"/>
+    <row r="12" spans="1:3">
+      <c r="C12" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3518,17 +5288,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3539,18 +5310,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3558,10 +5329,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3569,7 +5340,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3577,16 +5348,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.85546875" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3597,88 +5369,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3695,15 +5408,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3714,18 +5428,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3733,10 +5447,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3749,6 +5463,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Creation Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB8BF19-4EE2-4D39-B907-89BA8F1901C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782E1800-C6D8-4D4A-88B6-DA65255C44BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="28" activeTab="30" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="18" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="78">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>For-profit organizations;Individuals</t>
+  </si>
+  <si>
+    <t>For-profit organizations;Individuals;Public Schools</t>
   </si>
 </sst>
 </file>
@@ -432,9 +435,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -472,7 +475,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -578,7 +581,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -720,7 +723,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1551,7 +1554,7 @@
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2271,7 +2274,7 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB986768-EEC8-4579-9001-144D172E4C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D515A4C-E06E-4F18-B126-6B8071ED5740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" tabRatio="795" firstSheet="15" activeTab="20" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="29" activeTab="30" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -758,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="59.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1542,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,9 +1710,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +1973,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2109,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2410,10 +2410,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2579,10 +2579,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2749,11 +2749,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2920,11 +2920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +2985,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3154,10 +3154,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3323,9 +3323,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3492,9 +3492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3661,9 +3661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3829,10 +3829,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +3987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4157,11 +4157,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4327,9 +4327,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4495,10 +4495,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4533,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4703,10 +4703,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4752,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4921,9 +4921,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +4962,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5132,9 +5132,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5289,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5353,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5413,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5472,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D515A4C-E06E-4F18-B126-6B8071ED5740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2083F2D-9332-4551-A38F-A3DF9159218E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="29" activeTab="30" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="15" activeTab="16" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2083F2D-9332-4551-A38F-A3DF9159218E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A8F41-48FD-483D-B842-1FFF091AF533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="15" activeTab="16" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A8F41-48FD-483D-B842-1FFF091AF533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B974E23-18C0-4B14-AB1B-AFF7E396EC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="15" activeTab="16" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="19" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="92">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -330,13 +330,37 @@
   </si>
   <si>
     <t>DetailedBudgetingRequired__c</t>
+  </si>
+  <si>
+    <t>Department of Health</t>
+  </si>
+  <si>
+    <t>Departmental Description</t>
+  </si>
+  <si>
+    <t>AdministrationBureauUnit__c</t>
+  </si>
+  <si>
+    <t>Office of Victim Services and Justice (OVSJG)</t>
+  </si>
+  <si>
+    <t>LinkforAdditionalInformation__c</t>
+  </si>
+  <si>
+    <t>www.reisystems.in</t>
+  </si>
+  <si>
+    <t>AdditionalInformation__c</t>
+  </si>
+  <si>
+    <t>Additional Information for Department</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +420,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -418,7 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -441,6 +471,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -758,10 +789,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +853,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -848,7 +879,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -859,7 +890,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -886,9 +917,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.6328125" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +977,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="65.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="65.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1037,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.33203125" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" customWidth="1"/>
+    <col min="3" max="3" width="46.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1096,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.6328125" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1156,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1214,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="59.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.36328125" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1273,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1334,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1395,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1513,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
-    <col min="3" max="3" width="62.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" customWidth="1"/>
+    <col min="3" max="3" width="62.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1541,15 +1572,15 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1560,7 +1591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1568,10 +1599,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1582,18 +1613,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1604,7 +1635,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1615,7 +1646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1626,7 +1657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1637,7 +1668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1648,61 +1679,90 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13">
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="G14">
-        <v>0</v>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C9" r:id="rId1" xr:uid="{F4D31CA5-8F43-42CF-8982-056FC1AEE3F1}"/>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{12588E08-AB48-4DCB-84F4-BB1F589890A9}"/>
+    <hyperlink ref="C11" r:id="rId2" xr:uid="{6D01E2D7-A1D6-42DA-A1F3-372D067CA48A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1710,9 +1770,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1885,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +2033,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2169,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2218,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2300,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2410,10 +2470,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2579,10 +2639,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2749,11 +2809,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2920,11 +2980,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +3045,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3154,10 +3214,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3323,9 +3383,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3492,9 +3552,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3661,9 +3721,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3683,10 +3743,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3694,10 +3754,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3705,7 +3765,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -3716,7 +3776,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -3741,7 +3801,7 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3829,10 +3889,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +4047,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.6328125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4157,11 +4217,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4327,9 +4387,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4495,10 +4555,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4593,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4703,10 +4763,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4812,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4921,9 +4981,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +5022,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5132,9 +5192,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5349,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5413,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5473,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5532,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B974E23-18C0-4B14-AB1B-AFF7E396EC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0297B178-4488-4D4A-B574-A1444A6CE334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="19" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="8" activeTab="9" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -332,9 +332,6 @@
     <t>DetailedBudgetingRequired__c</t>
   </si>
   <si>
-    <t>Department of Health</t>
-  </si>
-  <si>
     <t>Departmental Description</t>
   </si>
   <si>
@@ -354,13 +351,16 @@
   </si>
   <si>
     <t>Additional Information for Department</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,6 +426,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF067D17"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -448,7 +454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -472,6 +478,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -878,8 +887,8 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>84</v>
+      <c r="C2" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -889,8 +898,8 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>84</v>
+      <c r="C3" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1599,7 +1608,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1684,10 +1693,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>86</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1695,10 +1704,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1706,10 +1715,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>90</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0297B178-4488-4D4A-B574-A1444A6CE334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F06A7C1-C9A3-424A-A2AB-DEDFCEAA76B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="8" activeTab="9" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="795" firstSheet="15" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -333,12 +333,6 @@
   </si>
   <si>
     <t>Departmental Description</t>
-  </si>
-  <si>
-    <t>AdministrationBureauUnit__c</t>
-  </si>
-  <si>
-    <t>Office of Victim Services and Justice (OVSJG)</t>
   </si>
   <si>
     <t>LinkforAdditionalInformation__c</t>
@@ -888,7 +882,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -899,7 +893,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1581,7 +1575,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
@@ -1695,7 +1689,7 @@
       <c r="B10" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="3" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1706,19 +1700,19 @@
       <c r="B11" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="12" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>90</v>
+        <v>16</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12">
+        <v>10000</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1726,10 +1720,10 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13">
-        <v>10000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1737,10 +1731,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14">
-        <v>100000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1748,27 +1742,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16">
         <v>10000</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C9" r:id="rId1" xr:uid="{12588E08-AB48-4DCB-84F4-BB1F589890A9}"/>
-    <hyperlink ref="C11" r:id="rId2" xr:uid="{6D01E2D7-A1D6-42DA-A1F3-372D067CA48A}"/>
+    <hyperlink ref="C10" r:id="rId2" xr:uid="{6D01E2D7-A1D6-42DA-A1F3-372D067CA48A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GG_Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A8F41-48FD-483D-B842-1FFF091AF533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD20AD8B-F535-4660-BDAC-63416B311088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="15" activeTab="16" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="795" firstSheet="20" activeTab="25" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -758,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="65.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="65.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.33203125" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="59.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
-    <col min="3" max="3" width="62.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1542,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,9 +1710,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +1973,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2109,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2410,10 +2410,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2579,10 +2579,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2749,11 +2749,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2920,11 +2920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +2985,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3154,10 +3154,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3323,9 +3323,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3492,9 +3492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3661,9 +3661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3829,10 +3829,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +3987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4157,11 +4157,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4327,9 +4327,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4495,10 +4495,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4533,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4703,10 +4703,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4752,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4921,9 +4921,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +4962,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5132,9 +5132,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5289,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5353,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5413,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5472,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GG_Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD20AD8B-F535-4660-BDAC-63416B311088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836DB008-0C5E-42A0-BF15-31C7A328665A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="795" firstSheet="20" activeTab="25" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17A8F41-48FD-483D-B842-1FFF091AF533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77761580-1E5E-4B82-9467-19C8AF3E0CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="15" activeTab="16" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="18" activeTab="18" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="85">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -330,13 +330,16 @@
   </si>
   <si>
     <t>DetailedBudgetingRequired__c</t>
+  </si>
+  <si>
+    <t>Business or Organization</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,13 +382,6 @@
       <family val="3"/>
     </font>
     <font>
-      <b/>
-      <sz val="9.8000000000000007"/>
-      <color rgb="FF297BDE"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
@@ -418,7 +414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -433,14 +429,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -758,14 +751,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -776,7 +769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -787,18 +780,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -809,7 +802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C12" s="5"/>
     </row>
   </sheetData>
@@ -822,14 +815,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -840,7 +833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -851,7 +844,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -862,7 +855,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -873,7 +866,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" s="5"/>
     </row>
   </sheetData>
@@ -886,14 +879,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.6640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -904,7 +897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -915,7 +908,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -926,7 +919,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -946,13 +939,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" customWidth="1"/>
     <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -963,7 +956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -974,7 +967,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -985,7 +978,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1006,13 +999,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="31.33203125" customWidth="1"/>
     <col min="3" max="3" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1034,7 +1027,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1045,7 +1038,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1065,13 +1058,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.6640625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,7 +1075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1093,7 +1086,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1104,7 +1097,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1125,13 +1118,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1142,7 +1135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1153,7 +1146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1157,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1183,13 +1176,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1211,7 +1204,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1222,7 +1215,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1242,14 +1235,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1260,7 +1253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1271,7 +1264,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1282,7 +1275,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1303,14 +1296,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1321,7 +1314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1332,7 +1325,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1343,7 +1336,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1364,14 +1357,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1382,7 +1375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1393,18 +1386,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1415,18 +1408,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1437,7 +1430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1452,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1482,14 +1475,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.44140625" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" customWidth="1"/>
     <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1500,7 +1493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1511,18 +1504,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1542,14 +1535,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1560,7 +1553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1571,7 +1564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1579,10 +1572,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1593,7 +1586,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1604,7 +1597,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1615,7 +1608,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1626,7 +1619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1637,7 +1630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1648,7 +1641,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1659,7 +1652,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1670,7 +1663,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1681,7 +1674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1692,7 +1685,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G14">
         <v>0</v>
       </c>
@@ -1710,14 +1703,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +1721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1739,7 +1732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1743,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1761,7 +1754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1772,7 +1765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1783,7 +1776,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1794,7 +1787,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1805,7 +1798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1825,13 +1818,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1842,7 +1835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1853,7 +1846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1864,7 +1857,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1875,7 +1868,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1886,7 +1879,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1897,7 +1890,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1908,7 +1901,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1919,7 +1912,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1930,7 +1923,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1941,7 +1934,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1952,7 +1945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1973,13 +1966,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1990,7 +1983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +1994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2012,7 +2005,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2023,7 +2016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2034,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2045,7 +2038,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2056,7 +2049,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2067,7 +2060,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2078,7 +2071,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2089,7 +2082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2109,14 +2102,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2127,7 +2120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2138,7 +2131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2158,13 +2151,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2175,7 +2168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2186,7 +2179,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2197,7 +2190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2208,7 +2201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2219,7 +2212,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2240,14 +2233,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2269,7 +2262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2280,7 +2273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2291,7 +2284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2302,7 +2295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2313,7 +2306,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2324,7 +2317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2335,7 +2328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2346,7 +2339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2357,7 +2350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2368,7 +2361,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2379,7 +2372,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2390,7 +2383,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2410,13 +2403,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2427,7 +2420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2438,7 +2431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2449,7 +2442,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2460,7 +2453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2471,7 +2464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2482,7 +2475,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2493,7 +2486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2504,7 +2497,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2515,7 +2508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2526,7 +2519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2537,7 +2530,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2548,7 +2541,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2559,7 +2552,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2579,13 +2572,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2596,7 +2589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2607,7 +2600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2618,7 +2611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2629,7 +2622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2640,7 +2633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2651,7 +2644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2662,7 +2655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2673,7 +2666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2684,7 +2677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2695,7 +2688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2706,7 +2699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2717,7 +2710,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2728,7 +2721,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2749,14 +2742,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2767,7 +2760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2778,7 +2771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2789,7 +2782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2800,7 +2793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2811,7 +2804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2822,7 +2815,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2833,7 +2826,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2844,7 +2837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2855,7 +2848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2866,7 +2859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2877,7 +2870,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2888,7 +2881,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2899,7 +2892,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2920,14 +2913,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2938,7 +2931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2949,7 +2942,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2960,7 +2953,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2971,7 +2964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
     </row>
@@ -2985,13 +2978,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3002,7 +2995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3013,7 +3006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3024,7 +3017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3035,7 +3028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3046,7 +3039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3057,7 +3050,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3068,7 +3061,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3079,7 +3072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3090,7 +3083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3101,7 +3094,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3112,7 +3105,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3123,7 +3116,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3134,11 +3127,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -3154,13 +3147,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3171,7 +3164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3182,7 +3175,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3193,7 +3186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3204,7 +3197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3215,7 +3208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3226,7 +3219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3237,7 +3230,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3248,7 +3241,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3259,7 +3252,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3270,7 +3263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3281,7 +3274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3292,7 +3285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3303,7 +3296,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -3323,13 +3316,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3340,7 +3333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3351,7 +3344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3362,7 +3355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3373,7 +3366,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3384,7 +3377,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3395,7 +3388,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3406,7 +3399,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3417,7 +3410,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3428,7 +3421,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3439,7 +3432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3450,7 +3443,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3461,7 +3454,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3472,7 +3465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -3492,13 +3485,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3509,7 +3502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3520,7 +3513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3531,7 +3524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3542,7 +3535,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3553,7 +3546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3564,7 +3557,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3575,7 +3568,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3586,7 +3579,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3597,7 +3590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3608,7 +3601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3619,7 +3612,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3630,7 +3623,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3641,7 +3634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -3661,13 +3654,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3678,7 +3671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3689,7 +3682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3700,7 +3693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3711,7 +3704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3722,7 +3715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3733,7 +3726,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3744,7 +3737,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3755,7 +3748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3766,7 +3759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3777,7 +3770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3788,7 +3781,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3799,7 +3792,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3810,7 +3803,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -3829,13 +3822,13 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3846,7 +3839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3857,7 +3850,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3868,7 +3861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3879,7 +3872,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3890,7 +3883,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3901,7 +3894,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -3912,7 +3905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3923,7 +3916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -3934,7 +3927,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -3945,7 +3938,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -3956,7 +3949,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -3967,7 +3960,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -3987,14 +3980,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4005,7 +3998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4016,7 +4009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4027,7 +4020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4038,7 +4031,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4049,7 +4042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4060,7 +4053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4071,7 +4064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4082,7 +4075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4093,7 +4086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4104,7 +4097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -4115,7 +4108,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -4126,7 +4119,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -4137,7 +4130,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4157,14 +4150,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="2" max="2" width="24.44140625" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4175,7 +4168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4186,7 +4179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4197,7 +4190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4208,7 +4201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4219,7 +4212,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4230,7 +4223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4241,7 +4234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4252,7 +4245,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4263,7 +4256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4274,7 +4267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -4285,7 +4278,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -4296,7 +4289,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -4307,7 +4300,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4327,13 +4320,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4344,7 +4337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4355,7 +4348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4366,7 +4359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4377,7 +4370,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4388,7 +4381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4399,7 +4392,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4410,7 +4403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4421,7 +4414,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4432,7 +4425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4443,7 +4436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -4454,7 +4447,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -4465,7 +4458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -4476,7 +4469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4495,14 +4488,14 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4513,7 +4506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4533,13 +4526,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4550,7 +4543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4561,7 +4554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4572,7 +4565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4583,7 +4576,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4594,7 +4587,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4605,7 +4598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4616,7 +4609,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4627,7 +4620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4638,7 +4631,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4649,7 +4642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -4660,7 +4653,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -4671,7 +4664,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -4682,7 +4675,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4703,13 +4696,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4720,7 +4713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4731,7 +4724,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4752,13 +4745,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4769,7 +4762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4780,7 +4773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4791,7 +4784,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4802,7 +4795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -4813,7 +4806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -4824,7 +4817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -4835,7 +4828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -4846,7 +4839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -4857,7 +4850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -4868,7 +4861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -4879,7 +4872,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -4890,7 +4883,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -4901,7 +4894,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -4921,14 +4914,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4939,7 +4932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4950,7 +4943,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" s="3"/>
     </row>
   </sheetData>
@@ -4962,14 +4955,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4980,7 +4973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4991,7 +4984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5002,7 +4995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5013,7 +5006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -5024,7 +5017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -5035,7 +5028,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -5046,7 +5039,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -5057,7 +5050,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -5068,7 +5061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -5079,7 +5072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -5090,7 +5083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -5101,7 +5094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5112,7 +5105,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -5132,14 +5125,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5150,7 +5143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5161,7 +5154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -5172,7 +5165,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -5183,7 +5176,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5194,7 +5187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5205,7 +5198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -5216,7 +5209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -5227,7 +5220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -5238,7 +5231,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -5249,7 +5242,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5260,7 +5253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -5271,7 +5264,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G13">
         <v>0</v>
       </c>
@@ -5289,14 +5282,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5307,7 +5300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5318,7 +5311,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5329,7 +5322,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5340,7 +5333,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C12" s="5"/>
     </row>
   </sheetData>
@@ -5353,14 +5346,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.44140625" customWidth="1"/>
     <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5371,7 +5364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5382,7 +5375,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5393,7 +5386,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5413,13 +5406,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5430,7 +5423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5441,7 +5434,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5452,7 +5445,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5472,13 +5465,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5489,7 +5482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5500,7 +5493,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5511,7 +5504,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GG_Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2024 July Aug Sept\3.0\prod san2\product_lwctestDilipTemp\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836DB008-0C5E-42A0-BF15-31C7A328665A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1830DB67-0B1C-464C-B5D4-7CA2D90E23AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="795" firstSheet="20" activeTab="25" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="795" firstSheet="27" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -758,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.7265625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="65.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="3" max="3" width="46.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.7265625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="59.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="3" max="3" width="62.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1542,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,9 +1710,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +1973,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2109,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2410,10 +2410,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2579,10 +2579,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2601,10 +2601,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2612,10 +2612,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2749,11 +2749,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2772,10 +2772,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2783,10 +2783,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2920,11 +2920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +2985,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3007,10 +3007,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3018,10 +3018,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3154,10 +3154,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3323,9 +3323,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3492,9 +3492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3661,9 +3661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3829,10 +3829,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +3987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4157,11 +4157,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4327,9 +4327,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4495,10 +4495,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4533,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4703,10 +4703,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4752,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4921,9 +4921,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +4962,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5132,9 +5132,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5289,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5353,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.453125" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5413,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5472,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GG_Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836DB008-0C5E-42A0-BF15-31C7A328665A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7431AC7-CDD5-4D4D-9D76-3A5662F23E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="795" firstSheet="20" activeTab="25" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="26" activeTab="28" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -418,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -441,6 +441,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -758,10 +761,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,9 +889,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +949,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1009,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1068,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1128,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1186,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="59.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1245,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1306,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1367,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1485,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1542,9 +1545,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,9 +1713,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1828,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +1976,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2112,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2161,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2243,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2263,10 +2266,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2274,10 +2277,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3" s="12">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2410,10 +2413,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2579,10 +2582,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2601,10 +2604,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2612,10 +2615,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3" s="12">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2749,11 +2752,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2772,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2783,10 +2786,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2920,11 +2923,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +2988,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3154,10 +3157,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3323,9 +3326,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3492,9 +3495,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3661,9 +3664,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3829,10 +3832,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +3990,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4157,11 +4160,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4327,9 +4330,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4495,10 +4498,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4536,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4703,10 +4706,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4755,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4921,9 +4924,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +4965,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5132,9 +5135,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5292,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5356,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5416,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5475,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GG_Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836DB008-0C5E-42A0-BF15-31C7A328665A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4200FD86-0D82-4323-A57E-3589A0D2662B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="795" firstSheet="20" activeTab="25" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="42" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -758,10 +758,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -822,10 +822,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,9 +886,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -946,10 +946,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1006,10 +1006,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1065,9 +1065,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1125,10 +1125,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1183,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="59.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1242,10 +1242,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1303,10 +1303,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1364,11 +1364,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1482,11 +1482,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1542,9 +1542,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1710,9 +1710,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1825,10 +1825,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1973,10 +1973,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2109,11 +2109,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2158,10 +2158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,11 +2240,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2263,10 +2263,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2274,10 +2274,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2410,10 +2410,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2432,10 +2432,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2443,10 +2443,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2579,10 +2579,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2601,10 +2601,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2612,10 +2612,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2749,11 +2749,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2772,10 +2772,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2783,10 +2783,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2920,11 +2920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2985,9 +2985,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3007,10 +3007,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3018,10 +3018,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3154,10 +3154,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3176,10 +3176,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3187,10 +3187,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3323,9 +3323,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3345,10 +3345,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3356,10 +3356,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3492,9 +3492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3514,10 +3514,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3525,10 +3525,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3661,9 +3661,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3683,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3694,7 +3694,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -3705,10 +3705,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3829,10 +3829,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3987,10 +3987,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4021,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4157,11 +4157,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4180,10 +4180,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4191,10 +4191,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4327,9 +4327,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4349,10 +4349,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4360,10 +4360,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4495,10 +4495,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4533,9 +4533,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4555,10 +4555,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4566,10 +4566,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4703,10 +4703,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4752,9 +4752,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4774,10 +4774,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4785,10 +4785,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4921,9 +4921,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -4962,10 +4962,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4985,10 +4985,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4996,10 +4996,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5132,9 +5132,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5289,10 +5289,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5353,11 +5353,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5413,10 +5413,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5472,10 +5472,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4200FD86-0D82-4323-A57E-3589A0D2662B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9734CA52-4BE2-4ECE-A9A0-A9C07D495888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="42" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="7" activeTab="7" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="87">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -320,16 +320,25 @@
     <t>EstimatedNumberOfAwards__c</t>
   </si>
   <si>
-    <t>Individuals</t>
-  </si>
-  <si>
-    <t>PreApplicationDueDate__c</t>
-  </si>
-  <si>
     <t>MaxApplicationsAllowed__c</t>
   </si>
   <si>
     <t>DetailedBudgetingRequired__c</t>
+  </si>
+  <si>
+    <t>IsDirectGrant_VA__c</t>
+  </si>
+  <si>
+    <t>For-Profit Organization (Other than Small Business)</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>ApplicationDeadlineWithDateTime__c</t>
+  </si>
+  <si>
+    <t>IsPriorityRequired_VA__c</t>
   </si>
 </sst>
 </file>
@@ -873,6 +882,17 @@
         <v>47</v>
       </c>
     </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="9" spans="1:3">
       <c r="C9" s="5"/>
     </row>
@@ -1541,7 +1561,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -1579,7 +1599,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1590,7 +1610,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1650,13 +1670,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10">
-        <v>1000</v>
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1664,10 +1684,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1675,10 +1695,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1686,14 +1706,25 @@
         <v>16</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="G14">
+    <row r="15" spans="1:7">
+      <c r="G15">
         <v>0</v>
       </c>
     </row>
@@ -1754,8 +1785,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>71</v>
+      <c r="B4" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1828,7 +1859,7 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1861,7 +1892,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1872,15 +1903,15 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>71</v>
+      <c r="B5" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="C5">
         <v>45</v>
@@ -1891,10 +1922,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1902,10 +1933,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1913,7 +1944,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -2239,7 +2270,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
@@ -2307,10 +2338,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2318,7 +2349,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -2329,7 +2360,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -2340,10 +2371,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2351,10 +2382,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2362,42 +2393,20 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2984,7 +2993,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -3051,7 +3060,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -3062,10 +3071,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3073,7 +3082,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -3084,10 +3093,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3095,10 +3104,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3106,7 +3115,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -3116,32 +3125,10 @@
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="B12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3660,7 +3647,7 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -3727,7 +3714,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -3738,7 +3725,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -3749,7 +3736,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -3760,10 +3747,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3771,10 +3758,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3782,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -3792,32 +3779,10 @@
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4156,7 +4121,7 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -4224,7 +4189,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -4235,10 +4200,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4246,10 +4211,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4257,10 +4222,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4268,10 +4233,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4279,7 +4244,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -4289,32 +4254,10 @@
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -4518,7 +4461,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -5412,7 +5355,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
@@ -5461,6 +5404,17 @@
       </c>
       <c r="C4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9734CA52-4BE2-4ECE-A9A0-A9C07D495888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D26784-C2ED-484B-ACAD-2D22BF8F059C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="7" activeTab="7" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="14" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -1561,7 +1561,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -1569,7 +1569,7 @@
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1613,18 +1613,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>71</v>
+      <c r="B5" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="C5">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1721,11 +1721,6 @@
       </c>
       <c r="C14">
         <v>10000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="G15">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D26784-C2ED-484B-ACAD-2D22BF8F059C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A17D662-8E3C-49A7-AADE-F22C6292981E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="14" activeTab="19" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="29" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -890,7 +890,7 @@
         <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5409,7 +5409,7 @@
         <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A17D662-8E3C-49A7-AADE-F22C6292981E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5875C9A-4D6F-46DF-8ED6-CF6918FCD666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="29" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="28" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="88">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>IsPriorityRequired_VA__c</t>
+  </si>
+  <si>
+    <t>PaymentsRequired__c</t>
   </si>
 </sst>
 </file>
@@ -2988,7 +2991,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -3088,10 +3091,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3099,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -3110,7 +3113,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -3120,10 +3123,21 @@
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3642,7 +3656,7 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -3742,10 +3756,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3753,7 +3767,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -3764,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -3774,10 +3788,21 @@
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>66</v>
       </c>
     </row>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4200FD86-0D82-4323-A57E-3589A0D2662B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35539BAE-3949-4019-BC7B-FF427D148EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="42" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="29" activeTab="33" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA ORG NEW\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A17D662-8E3C-49A7-AADE-F22C6292981E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0695D7E-0053-4823-9EB6-B7F6EC43C9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="29" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="29" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="88">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>IsPriorityRequired_VA__c</t>
+  </si>
+  <si>
+    <t>PaymentsRequired__c</t>
   </si>
 </sst>
 </file>
@@ -2988,7 +2991,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -3088,7 +3091,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -3099,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -3109,21 +3112,10 @@
       <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="B11" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>66</v>
       </c>
     </row>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35539BAE-3949-4019-BC7B-FF427D148EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0E8D16-E86E-4576-A8E4-2662C4D5336F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="29" activeTab="33" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -47,15 +47,19 @@
     <sheet name="Creation Second Modal for App" sheetId="25" r:id="rId32"/>
     <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId33"/>
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId35"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId36"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId37"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId38"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId39"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId40"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId41"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId42"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId43"/>
+    <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId36"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId37"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId38"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId39"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId40"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId41"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId42"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId43"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId44"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId45"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId46"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId47"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="127">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -330,6 +334,135 @@
   </si>
   <si>
     <t>DetailedBudgetingRequired__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Leads</t>
+  </si>
+  <si>
+    <t>OpportunityTitle__c</t>
+  </si>
+  <si>
+    <t>OpportunityNumber__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Opp No</t>
+  </si>
+  <si>
+    <t>CloseDate__c</t>
+  </si>
+  <si>
+    <t>FederalAgency__c</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>EligibleApplicants__c</t>
+  </si>
+  <si>
+    <t>For profit organizations other than small businesses</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>CostSharing__c</t>
+  </si>
+  <si>
+    <t>OpportunityCategory__c</t>
+  </si>
+  <si>
+    <t>Earmark</t>
+  </si>
+  <si>
+    <t>FundingInstrumentType__c</t>
+  </si>
+  <si>
+    <t>Cooperative Agreement</t>
+  </si>
+  <si>
+    <t>CategoryOfFundingActivity__c</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>ArchiveDate__c</t>
+  </si>
+  <si>
+    <t>EstimatedTotalProgramFunding__c</t>
+  </si>
+  <si>
+    <t>Relevance__c</t>
+  </si>
+  <si>
+    <t>3 - Medium</t>
+  </si>
+  <si>
+    <t>Impact__c</t>
+  </si>
+  <si>
+    <t>EstimatedProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>EstimatedProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>LetterOfIntentRequired__c</t>
+  </si>
+  <si>
+    <t>LetterOfIntentDueDate__c</t>
+  </si>
+  <si>
+    <t>AnticipatedAwardDate__c</t>
+  </si>
+  <si>
+    <t>Cash and Non-Cash Match</t>
+  </si>
+  <si>
+    <t>RateOfMatch__c</t>
+  </si>
+  <si>
+    <t>MatchSource__c</t>
+  </si>
+  <si>
+    <t>External Source</t>
+  </si>
+  <si>
+    <t>ProgramType__c</t>
+  </si>
+  <si>
+    <t>Additive</t>
+  </si>
+  <si>
+    <t>DoesGrantAllowIndirect__c</t>
+  </si>
+  <si>
+    <t>FundingAgencyRestriction__c</t>
+  </si>
+  <si>
+    <t>AgencyStandardOrOther__c</t>
+  </si>
+  <si>
+    <t>Federally approved indirect rate</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>HaveWeReceivedAwardFromProgram__c</t>
+  </si>
+  <si>
+    <t>PastFundingDescription__c</t>
+  </si>
+  <si>
+    <t>ProbabilityofWinningreceivingaGrant__c</t>
+  </si>
+  <si>
+    <t>AwardProbabilityExplanation__c</t>
   </si>
 </sst>
 </file>
@@ -418,7 +551,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -441,6 +574,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3827,6 +3966,537 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D5F1C4-68E1-4C20-A92E-5B34A98159BC}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -3976,552 +4646,6 @@
       </c>
       <c r="C13" s="7" t="s">
         <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
-  <sheetPr codeName="Sheet32"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
-  <sheetPr codeName="Sheet33"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
-  <sheetPr codeName="Sheet34"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4700,6 +4824,552 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
+  <sheetPr codeName="Sheet32"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
+  <sheetPr codeName="Sheet33"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
+  <sheetPr codeName="Sheet34"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -4748,7 +5418,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -4917,7 +5587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
@@ -4958,7 +5628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0E8D16-E86E-4576-A8E4-2662C4D5336F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCB337D-8634-4FA0-8FF0-ACF909EDDCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="147">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -463,6 +463,66 @@
   </si>
   <si>
     <t>AwardProbabilityExplanation__c</t>
+  </si>
+  <si>
+    <t>BusinessandTechnicaldomainKnowledge__c</t>
+  </si>
+  <si>
+    <t>DetailTechnicalKnowledge__c</t>
+  </si>
+  <si>
+    <t>SkillSets__c</t>
+  </si>
+  <si>
+    <t>ExplainRequiredResources__c</t>
+  </si>
+  <si>
+    <t>NecessarySystemsAndFinancialTools__c</t>
+  </si>
+  <si>
+    <t>ExplainRequiredRequirements__c</t>
+  </si>
+  <si>
+    <t>LevelofEffort__c</t>
+  </si>
+  <si>
+    <t>Sixty</t>
+  </si>
+  <si>
+    <t>EstimatedFTEToBeHired__c</t>
+  </si>
+  <si>
+    <t>Eighty</t>
+  </si>
+  <si>
+    <t>LeadAgencyAgreedUpon__c</t>
+  </si>
+  <si>
+    <t>CollaborationandWorkShare__c</t>
+  </si>
+  <si>
+    <t>DescribeRequiredCollaboration__c</t>
+  </si>
+  <si>
+    <t>MaintenanceEffortRequire__c</t>
+  </si>
+  <si>
+    <t>StatutoryMaintenanceOfEffort__c</t>
+  </si>
+  <si>
+    <t>LimitOnAdministrativeRate__c</t>
+  </si>
+  <si>
+    <t>AdminLimitation__c</t>
+  </si>
+  <si>
+    <t>ProgramSustainability__c</t>
+  </si>
+  <si>
+    <t>LegalRequirementOrOtherCertification__c</t>
+  </si>
+  <si>
+    <t>RichTextArea1__c</t>
   </si>
 </sst>
 </file>
@@ -4242,9 +4302,10 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -4448,7 +4509,7 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" t="s">
         <v>122</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -4459,7 +4520,7 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" t="s">
         <v>122</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -4470,7 +4531,7 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" t="s">
         <v>122</v>
       </c>
       <c r="B21" s="11" t="s">
@@ -4481,13 +4542,222 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" t="s">
         <v>122</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>126</v>
       </c>
       <c r="C22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" t="s">
         <v>94</v>
       </c>
     </row>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCB337D-8634-4FA0-8FF0-ACF909EDDCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23129BE-9EEE-4716-9C11-16EB24282214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="35" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="146">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -457,9 +457,6 @@
   </si>
   <si>
     <t>PastFundingDescription__c</t>
-  </si>
-  <si>
-    <t>ProbabilityofWinningreceivingaGrant__c</t>
   </si>
   <si>
     <t>AwardProbabilityExplanation__c</t>
@@ -611,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -635,9 +632,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4302,7 +4296,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -4537,8 +4531,8 @@
       <c r="B21" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="13">
-        <v>0.5</v>
+      <c r="C21" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -4549,7 +4543,7 @@
         <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4560,7 +4554,7 @@
         <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4571,7 +4565,7 @@
         <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4582,7 +4576,7 @@
         <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4593,7 +4587,7 @@
         <v>130</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -4604,7 +4598,7 @@
         <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -4615,7 +4609,7 @@
         <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -4623,10 +4617,10 @@
         <v>122</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -4634,10 +4628,10 @@
         <v>122</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -4659,7 +4653,7 @@
         <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -4667,10 +4661,10 @@
         <v>122</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4678,7 +4672,7 @@
         <v>122</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
@@ -4692,7 +4686,7 @@
         <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -4703,7 +4697,7 @@
         <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4713,8 +4707,8 @@
       <c r="B37" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
+      <c r="C37" s="12">
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -4724,8 +4718,8 @@
       <c r="B38" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C38" s="12">
-        <v>70</v>
+      <c r="C38" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4750,19 +4744,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" t="s">
-        <v>94</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23129BE-9EEE-4716-9C11-16EB24282214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6807EFB0-4534-4936-BF09-BCE36BC7B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="35" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6807EFB0-4534-4936-BF09-BCE36BC7B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA5CA7F-8DD2-46FE-A2C8-53F4C9171581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="35" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -499,18 +499,6 @@
   </si>
   <si>
     <t>DescribeRequiredCollaboration__c</t>
-  </si>
-  <si>
-    <t>MaintenanceEffortRequire__c</t>
-  </si>
-  <si>
-    <t>StatutoryMaintenanceOfEffort__c</t>
-  </si>
-  <si>
-    <t>LimitOnAdministrativeRate__c</t>
-  </si>
-  <si>
-    <t>AdminLimitation__c</t>
   </si>
   <si>
     <t>ProgramSustainability__c</t>
@@ -4296,7 +4284,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -4661,10 +4649,10 @@
         <v>122</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -4672,10 +4660,10 @@
         <v>122</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -4683,64 +4671,9 @@
         <v>122</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>122</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>122</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C37" s="12">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>122</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>122</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C40" t="s">
         <v>94</v>
       </c>
     </row>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA5CA7F-8DD2-46FE-A2C8-53F4C9171581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6038BC8B-63C0-4851-9C1A-73BED1AABC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="35" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -4388,7 +4388,7 @@
         <v>111</v>
       </c>
       <c r="C9">
-        <v>150</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6038BC8B-63C0-4851-9C1A-73BED1AABC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA721A66-D20D-4A26-A3C6-12C327811F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="37" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="38" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -51,15 +51,16 @@
     <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId36"/>
     <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId37"/>
     <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId38"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId39"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId40"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId41"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId42"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId43"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId44"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId45"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId46"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId47"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId39"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId40"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId41"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId42"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId43"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId44"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId45"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId46"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId47"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId48"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4684,12 +4685,12 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
-  <dimension ref="A1:C13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4705,42 +4706,42 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
@@ -4749,90 +4750,321 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8">
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>66</v>
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5011,6 +5243,163 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
@@ -5180,7 +5569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
@@ -5350,7 +5739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
@@ -5519,7 +5908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5556,7 +5945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -5605,7 +5994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -5774,7 +6163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
@@ -5815,7 +6204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA721A66-D20D-4A26-A3C6-12C327811F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F733FF-6E6E-4A31-93F8-229FE45A32F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="38" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="36" activeTab="39" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -52,15 +52,16 @@
     <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId37"/>
     <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId38"/>
     <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId39"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId40"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId41"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId42"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId43"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId44"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId45"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId46"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId47"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId48"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId40"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId41"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId42"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId43"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId44"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId45"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId46"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId47"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId48"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId49"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -515,7 +516,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,6 +576,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -597,7 +604,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -623,6 +630,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5243,6 +5251,405 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5399,7 +5806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
@@ -5569,7 +5976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
@@ -5739,7 +6146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
@@ -5908,7 +6315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5945,7 +6352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -5994,7 +6401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -6163,7 +6570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
@@ -6204,7 +6611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F733FF-6E6E-4A31-93F8-229FE45A32F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65A6DF1-2DEB-43B8-A119-D78A4B288A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="36" activeTab="39" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="38" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -48,20 +48,22 @@
     <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId33"/>
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
     <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
-    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId36"/>
-    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId37"/>
-    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId38"/>
-    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId39"/>
-    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId40"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId41"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId42"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId43"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId44"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId45"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId46"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId47"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId48"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId49"/>
+    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId36"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId37"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId38"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId39"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId40"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId41"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId42"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId43"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId44"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId45"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId46"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId47"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId48"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId49"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId50"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId51"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4131,6 +4133,119 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4233,7 +4348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4291,7 +4406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4689,394 +4804,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>122</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>122</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>122</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5251,6 +4978,394 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5649,7 +5764,340 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5806,7 +6254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
@@ -5976,7 +6424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
@@ -6146,7 +6594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
@@ -6315,7 +6763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6352,7 +6800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -6401,7 +6849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -6563,217 +7011,6 @@
       </c>
       <c r="C14" s="7" t="s">
         <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
-  <sheetPr codeName="Sheet37"/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="C9" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
-  <sheetPr codeName="Sheet38"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -6935,6 +7172,217 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
+  <sheetPr codeName="Sheet37"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="C9" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
+  <sheetPr codeName="Sheet38"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65A6DF1-2DEB-43B8-A119-D78A4B288A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FF59AB-092C-4123-A3E7-A24F7992B1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="38" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="38" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FF59AB-092C-4123-A3E7-A24F7992B1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F0387-B449-4BE4-80FC-E0C69F059A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="34" activeTab="38" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="38" activeTab="39" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28318"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35539BAE-3949-4019-BC7B-FF427D148EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F0387-B449-4BE4-80FC-E0C69F059A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="29" activeTab="33" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="39" activeTab="39" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -47,17 +47,25 @@
     <sheet name="Creation Second Modal for App" sheetId="25" r:id="rId32"/>
     <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId33"/>
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId35"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId36"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId37"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId38"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId39"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId40"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId41"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId42"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId43"/>
+    <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
+    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId36"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId37"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId38"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId39"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId40"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId41"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId42"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId43"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId44"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId45"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId46"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId47"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId48"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId49"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId50"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId51"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -78,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -95,30 +103,81 @@
     <t>AnnouncementName__c</t>
   </si>
   <si>
+    <t>Automation Runtime Directed Announcement</t>
+  </si>
+  <si>
     <t>Program__c</t>
   </si>
   <si>
+    <t>Automation Permanent Internal Program For Admin User</t>
+  </si>
+  <si>
     <t>Budget_Category_Package__c</t>
   </si>
   <si>
     <t>Non-Construction</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Automation Runtime Formula Announcement</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program_NoFA</t>
+  </si>
+  <si>
+    <t>IsMatchRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>GranteeMatch__c</t>
+  </si>
+  <si>
+    <t>LaverageAllowed__c</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>IsProgramIncomeAnticipated__c</t>
+  </si>
+  <si>
+    <t>PreApplicationNeeded__c</t>
+  </si>
+  <si>
+    <t>RiskAssessment_Required__c</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>AreExpensesBuildIUpLevel__c</t>
+  </si>
+  <si>
+    <t>IsAdvancePermitted__c</t>
+  </si>
+  <si>
+    <t>IsNegotiationsAllowed__c</t>
+  </si>
+  <si>
+    <t>Allocationlevel__c</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Overview</t>
   </si>
   <si>
-    <t>IsMatchRequired__c</t>
-  </si>
-  <si>
-    <t>LaverageAllowed__c</t>
-  </si>
-  <si>
-    <t>IsProgramIncomeAnticipated__c</t>
-  </si>
-  <si>
-    <t>PreApplicationNeeded__c</t>
-  </si>
-  <si>
     <t>AnnouncementDescription__c</t>
   </si>
   <si>
@@ -128,13 +187,97 @@
     <t>EligibleApplicantTypes__c</t>
   </si>
   <si>
+    <t>For-profit organizations</t>
+  </si>
+  <si>
+    <t>ApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>QAAvailability__c</t>
+  </si>
+  <si>
+    <t>QSubmissionDeadline__c</t>
+  </si>
+  <si>
+    <t>AResponseDeadline__c</t>
+  </si>
+  <si>
+    <t>QAContactEmailAddress__c</t>
+  </si>
+  <si>
+    <t>deepika.vanamala@reisystems.com</t>
+  </si>
+  <si>
     <t>Financials</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>GranteeMatch__c</t>
+    <t>AwardFloor__c</t>
+  </si>
+  <si>
+    <t>AwardCeiling__c</t>
+  </si>
+  <si>
+    <t>EstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>TotalCommittedAmount__c</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program</t>
+  </si>
+  <si>
+    <t>Automation Runtime Competitive Announcement</t>
+  </si>
+  <si>
+    <t>Automation Runtime Competitive Announcement for Bulk</t>
+  </si>
+  <si>
+    <t>Automation Runtime Announcement for Pre-Application</t>
+  </si>
+  <si>
+    <t>Automation Runtime Competitive Past Announcement</t>
+  </si>
+  <si>
+    <t>Automation Runtime Announcement for Pre-App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Directed Announcement </t>
+  </si>
+  <si>
+    <t>Individuals</t>
+  </si>
+  <si>
+    <t>For-profit organizations;Individuals</t>
+  </si>
+  <si>
+    <t>PreApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>MaxApplicationsAllowed__c</t>
+  </si>
+  <si>
+    <t>fieldPreApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>fieldApplicationDueDate__c</t>
+  </si>
+  <si>
+    <t>fieldMaxApplicationsAllowed__c</t>
+  </si>
+  <si>
+    <t>fieldQAAvailability__c</t>
+  </si>
+  <si>
+    <t>fieldAwardFloor__c</t>
+  </si>
+  <si>
+    <t>fieldAwardCeiling__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>fieldTotalCommittedAmount__c</t>
   </si>
   <si>
     <t>BudgetStartDate__c</t>
@@ -143,200 +286,239 @@
     <t>BudgetEndDate__c</t>
   </si>
   <si>
+    <t>Name__c</t>
+  </si>
+  <si>
+    <t>Automation FO</t>
+  </si>
+  <si>
     <t>ReviewerRole__c</t>
   </si>
   <si>
     <t>Fiscal Reviewer</t>
   </si>
   <si>
-    <t>Name__c</t>
-  </si>
-  <si>
-    <t>Automation FO</t>
+    <t>Responsibility__c</t>
   </si>
   <si>
     <t>Review Financial details</t>
   </si>
   <si>
-    <t>Responsibility__c</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>RiskAssessment_Required__c</t>
+    <t>DueDate__c</t>
+  </si>
+  <si>
+    <t>AllowRecordEdit__c</t>
+  </si>
+  <si>
+    <t>By Applicant</t>
+  </si>
+  <si>
+    <t>By Applicant and Focus Area</t>
+  </si>
+  <si>
+    <t>OpportunityTitle__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Leads</t>
+  </si>
+  <si>
+    <t>OpportunityNumber__c</t>
+  </si>
+  <si>
+    <t>Automation Runtime Opp No</t>
+  </si>
+  <si>
+    <t>CloseDate__c</t>
+  </si>
+  <si>
+    <t>FederalAgency__c</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>EligibleApplicants__c</t>
+  </si>
+  <si>
+    <t>For profit organizations other than small businesses</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>CostSharing__c</t>
+  </si>
+  <si>
+    <t>OpportunityCategory__c</t>
+  </si>
+  <si>
+    <t>Earmark</t>
+  </si>
+  <si>
+    <t>FundingInstrumentType__c</t>
+  </si>
+  <si>
+    <t>Cooperative Agreement</t>
+  </si>
+  <si>
+    <t>CategoryOfFundingActivity__c</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>ArchiveDate__c</t>
+  </si>
+  <si>
+    <t>EstimatedTotalProgramFunding__c</t>
+  </si>
+  <si>
+    <t>Relevance__c</t>
+  </si>
+  <si>
+    <t>3 - Medium</t>
+  </si>
+  <si>
+    <t>Impact__c</t>
+  </si>
+  <si>
+    <t>Justification__c</t>
+  </si>
+  <si>
+    <t>EstimatedProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>EstimatedProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>LetterOfIntentRequired__c</t>
+  </si>
+  <si>
+    <t>LetterOfIntentDueDate__c</t>
+  </si>
+  <si>
+    <t>AnticipatedAwardDate__c</t>
+  </si>
+  <si>
+    <t>Cash and Non-Cash Match</t>
+  </si>
+  <si>
+    <t>RateOfMatch__c</t>
+  </si>
+  <si>
+    <t>MatchSource__c</t>
+  </si>
+  <si>
+    <t>External Source</t>
+  </si>
+  <si>
+    <t>ProgramType__c</t>
+  </si>
+  <si>
+    <t>Additive</t>
+  </si>
+  <si>
+    <t>DoesGrantAllowIndirect__c</t>
+  </si>
+  <si>
+    <t>FundingAgencyRestriction__c</t>
+  </si>
+  <si>
+    <t>AgencyStandardOrOther__c</t>
+  </si>
+  <si>
+    <t>Federally approved indirect rate</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>HaveWeReceivedAwardFromProgram__c</t>
+  </si>
+  <si>
+    <t>PastFundingDescription__c</t>
+  </si>
+  <si>
+    <t>AwardProbabilityExplanation__c</t>
+  </si>
+  <si>
+    <t>BusinessandTechnicaldomainKnowledge__c</t>
+  </si>
+  <si>
+    <t>DetailTechnicalKnowledge__c</t>
+  </si>
+  <si>
+    <t>SkillSets__c</t>
+  </si>
+  <si>
+    <t>ExplainRequiredResources__c</t>
+  </si>
+  <si>
+    <t>NecessarySystemsAndFinancialTools__c</t>
+  </si>
+  <si>
+    <t>ExplainRequiredRequirements__c</t>
+  </si>
+  <si>
+    <t>LevelofEffort__c</t>
+  </si>
+  <si>
+    <t>Sixty</t>
+  </si>
+  <si>
+    <t>EstimatedFTEToBeHired__c</t>
+  </si>
+  <si>
+    <t>Eighty</t>
+  </si>
+  <si>
+    <t>LeadAgencyAgreedUpon__c</t>
+  </si>
+  <si>
+    <t>CollaborationandWorkShare__c</t>
+  </si>
+  <si>
+    <t>DescribeRequiredCollaboration__c</t>
+  </si>
+  <si>
+    <t>ProgramSustainability__c</t>
+  </si>
+  <si>
+    <t>LegalRequirementOrOtherCertification__c</t>
+  </si>
+  <si>
+    <t>RichTextArea1__c</t>
+  </si>
+  <si>
+    <t>DetailedBudgetingRequired__c</t>
+  </si>
+  <si>
+    <t>Rating__c</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>ReviewComments__c</t>
+  </si>
+  <si>
+    <t>Reviewed</t>
+  </si>
+  <si>
+    <t>Automation</t>
   </si>
   <si>
     <t>WBSRequired__c</t>
-  </si>
-  <si>
-    <t>AreExpensesBuildIUpLevel__c</t>
-  </si>
-  <si>
-    <t>FocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>IsGoalsRequired__c</t>
-  </si>
-  <si>
-    <t>KPIsRequired__c</t>
-  </si>
-  <si>
-    <t>IsAdvancePermitted__c</t>
-  </si>
-  <si>
-    <t>IsNegotiationsAllowed__c</t>
-  </si>
-  <si>
-    <t>AllowRecordEdit__c</t>
-  </si>
-  <si>
-    <t>Rating__c</t>
-  </si>
-  <si>
-    <t>ReviewComments__c</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Reviewed</t>
-  </si>
-  <si>
-    <t>Automation Permanent Internal Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Directed Announcement </t>
-  </si>
-  <si>
-    <t>DueDate__c</t>
-  </si>
-  <si>
-    <t>Justification__c</t>
-  </si>
-  <si>
-    <t>Automation</t>
-  </si>
-  <si>
-    <t>deepika.vanamala@reisystems.com</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Automation Runtime Formula Announcement</t>
-  </si>
-  <si>
-    <t>Automation Runtime Competitive Announcement</t>
-  </si>
-  <si>
-    <t>Automation Runtime Announcement for Pre-Application</t>
-  </si>
-  <si>
-    <t>Automation Runtime Announcement for Pre-App</t>
-  </si>
-  <si>
-    <t>Automation Runtime Directed Announcement</t>
-  </si>
-  <si>
-    <t>Automation Runtime Competitive Past Announcement</t>
-  </si>
-  <si>
-    <t>fieldApplicationDueDate__c</t>
-  </si>
-  <si>
-    <t>fieldQAAvailability__c</t>
-  </si>
-  <si>
-    <t>fieldAwardFloor__c</t>
-  </si>
-  <si>
-    <t>fieldAwardCeiling__c</t>
-  </si>
-  <si>
-    <t>fieldTotalCommittedAmount__c</t>
-  </si>
-  <si>
-    <t>fieldEstimatedNumberOfAwards__c</t>
-  </si>
-  <si>
-    <t>fieldPreApplicationDueDate__c</t>
-  </si>
-  <si>
-    <t>fieldMaxApplicationsAllowed__c</t>
-  </si>
-  <si>
-    <t>Automation Permanent Internal Program For Admin User</t>
-  </si>
-  <si>
-    <t>Automation Runtime Competitive Announcement for Bulk</t>
-  </si>
-  <si>
-    <t>By Applicant and Focus Area</t>
-  </si>
-  <si>
-    <t>By Applicant</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Automation Permanent Internal Program_NoFA</t>
-  </si>
-  <si>
-    <t>For-profit organizations</t>
-  </si>
-  <si>
-    <t>For-profit organizations;Individuals</t>
-  </si>
-  <si>
-    <t>Allocationlevel__c</t>
-  </si>
-  <si>
-    <t>ApplicationDueDate__c</t>
-  </si>
-  <si>
-    <t>QAAvailability__c</t>
-  </si>
-  <si>
-    <t>QSubmissionDeadline__c</t>
-  </si>
-  <si>
-    <t>AResponseDeadline__c</t>
-  </si>
-  <si>
-    <t>QAContactEmailAddress__c</t>
-  </si>
-  <si>
-    <t>TotalCommittedAmount__c</t>
-  </si>
-  <si>
-    <t>AwardFloor__c</t>
-  </si>
-  <si>
-    <t>AwardCeiling__c</t>
-  </si>
-  <si>
-    <t>EstimatedNumberOfAwards__c</t>
-  </si>
-  <si>
-    <t>Individuals</t>
-  </si>
-  <si>
-    <t>PreApplicationDueDate__c</t>
-  </si>
-  <si>
-    <t>MaxApplicationsAllowed__c</t>
-  </si>
-  <si>
-    <t>DetailedBudgetingRequired__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +578,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -418,7 +606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -441,6 +629,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -460,9 +652,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -500,7 +692,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -606,7 +798,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -748,7 +940,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -758,10 +950,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -784,7 +976,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -792,10 +984,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -803,10 +995,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -822,10 +1014,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -848,7 +1040,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -856,10 +1048,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -867,10 +1059,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -886,9 +1078,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -912,7 +1104,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -920,10 +1112,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -931,10 +1123,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -946,10 +1138,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="65.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="65.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -971,7 +1163,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -979,10 +1171,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -990,10 +1182,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1006,10 +1198,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="31.33203125" customWidth="1"/>
-    <col min="3" max="3" width="46.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1031,7 +1223,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1039,10 +1231,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1050,10 +1242,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1065,9 +1257,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1090,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1098,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1109,10 +1301,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1125,10 +1317,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1150,7 +1342,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1158,10 +1350,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1169,10 +1361,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1183,10 +1375,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="59.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1208,7 +1400,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1216,10 +1408,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1227,10 +1419,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1242,10 +1434,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1268,7 +1460,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1276,10 +1468,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1287,10 +1479,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1303,10 +1495,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1329,7 +1521,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1337,10 +1529,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1348,10 +1540,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1364,11 +1556,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1384,32 +1576,32 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -1417,21 +1609,21 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1439,10 +1631,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1450,21 +1642,21 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -1482,11 +1674,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
-    <col min="3" max="3" width="62.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1508,7 +1700,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1516,10 +1708,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1527,10 +1719,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1542,9 +1734,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1562,43 +1754,43 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>45</v>
@@ -1606,21 +1798,21 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1628,10 +1820,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1639,21 +1831,21 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>1000</v>
@@ -1661,10 +1853,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C11">
         <v>10000</v>
@@ -1672,10 +1864,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1683,10 +1875,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C13">
         <v>10000</v>
@@ -1710,9 +1902,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1730,32 +1922,32 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1763,21 +1955,21 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1785,10 +1977,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>10000</v>
@@ -1796,10 +1988,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1807,10 +1999,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -1825,10 +2017,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1844,43 +2036,43 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>45</v>
@@ -1888,10 +2080,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>35</v>
@@ -1899,10 +2091,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1910,21 +2102,21 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -1932,10 +2124,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -1943,10 +2135,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1954,10 +2146,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>100000</v>
@@ -1973,10 +2165,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1992,32 +2184,32 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -2025,10 +2217,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2036,10 +2228,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2047,21 +2239,21 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>1000</v>
@@ -2069,10 +2261,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -2080,10 +2272,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2091,10 +2283,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>100000</v>
@@ -2109,11 +2301,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2132,7 +2324,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C2">
         <v>20</v>
@@ -2143,7 +2335,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>379</v>
@@ -2158,10 +2350,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2180,10 +2372,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2191,10 +2383,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2202,10 +2394,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2213,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>20</v>
@@ -2224,10 +2416,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2240,11 +2432,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2263,10 +2455,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2274,7 +2466,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2285,10 +2477,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2296,10 +2488,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2307,10 +2499,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2318,10 +2510,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2329,10 +2521,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2340,10 +2532,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2351,10 +2543,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2362,10 +2554,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2373,10 +2565,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2384,10 +2576,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2395,10 +2587,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2410,10 +2602,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2432,10 +2624,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2443,7 +2635,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2454,10 +2646,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2465,10 +2657,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2476,10 +2668,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2487,10 +2679,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2498,10 +2690,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2509,10 +2701,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2520,10 +2712,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2531,10 +2723,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2542,10 +2734,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2553,10 +2745,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2564,10 +2756,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2579,10 +2771,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2601,10 +2793,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2612,7 +2804,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2623,10 +2815,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2634,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2645,10 +2837,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2656,10 +2848,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2667,10 +2859,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2678,10 +2870,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2689,10 +2881,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2700,10 +2892,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2711,10 +2903,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2722,10 +2914,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2733,10 +2925,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2749,11 +2941,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2772,10 +2964,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2783,7 +2975,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2794,10 +2986,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2805,10 +2997,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2816,10 +3008,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2827,10 +3019,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2838,10 +3030,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2849,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2860,10 +3052,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2871,10 +3063,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2882,10 +3074,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2893,10 +3085,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2904,10 +3096,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2920,11 +3112,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.6640625" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2946,7 +3138,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2954,10 +3146,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2965,10 +3157,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2985,9 +3177,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3007,10 +3199,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3018,7 +3210,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -3029,10 +3221,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3040,10 +3232,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3051,10 +3243,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3062,10 +3254,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3073,10 +3265,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3084,10 +3276,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3095,10 +3287,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3106,10 +3298,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3117,10 +3309,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3128,10 +3320,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3139,10 +3331,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3154,10 +3346,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3176,10 +3368,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3187,7 +3379,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -3198,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3209,10 +3401,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3220,10 +3412,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3231,10 +3423,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3242,10 +3434,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3253,10 +3445,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3264,10 +3456,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3275,10 +3467,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3286,10 +3478,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3297,10 +3489,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3308,10 +3500,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3323,9 +3515,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3345,10 +3537,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3356,7 +3548,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -3367,10 +3559,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3378,10 +3570,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3389,10 +3581,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3400,10 +3592,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3411,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3422,10 +3614,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3433,10 +3625,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3444,10 +3636,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3455,10 +3647,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3466,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3477,10 +3669,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3492,9 +3684,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3514,10 +3706,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3525,7 +3717,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -3536,10 +3728,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3547,10 +3739,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3558,10 +3750,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3569,10 +3761,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3580,10 +3772,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3591,10 +3783,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3602,10 +3794,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3613,10 +3805,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3624,10 +3816,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3635,10 +3827,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3646,10 +3838,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3661,9 +3853,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3683,10 +3875,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3694,10 +3886,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3705,7 +3897,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -3716,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3727,10 +3919,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3738,10 +3930,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3749,10 +3941,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3760,10 +3952,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -3771,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3782,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3793,10 +3985,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3804,10 +3996,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3815,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3827,12 +4019,12 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D5F1C4-68E1-4C20-A92E-5B34A98159BC}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3851,10 +4043,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3862,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3873,10 +4065,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
+        <v>80</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3884,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3895,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3906,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3917,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3928,70 +4120,25 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
-  <sheetPr codeName="Sheet32"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4010,10 +4157,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4021,10 +4168,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4032,10 +4179,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
+        <v>80</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4043,10 +4190,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4054,10 +4201,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4065,10 +4212,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4076,10 +4223,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4087,65 +4234,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4154,14 +4246,13 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
-  <sheetPr codeName="Sheet33"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4177,145 +4268,79 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5">
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
+        <v>40</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>40</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
@@ -4324,13 +4349,12 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
-  <sheetPr codeName="Sheet34"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4346,145 +4370,35 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4493,13 +4407,13 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4515,17 +4429,381 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4533,9 +4811,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4555,10 +4833,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4566,7 +4844,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -4577,10 +4855,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4588,10 +4866,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4599,10 +4877,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4610,10 +4888,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4621,10 +4899,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4632,10 +4910,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4643,10 +4921,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4654,10 +4932,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4665,10 +4943,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4676,10 +4954,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4687,10 +4965,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -4700,13 +4978,12 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
-  <sheetPr codeName="Sheet35"/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4722,24 +4999,1848 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
+  <sheetPr codeName="Sheet32"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
+  <sheetPr codeName="Sheet33"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
+  <sheetPr codeName="Sheet34"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>40</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
+  <sheetPr codeName="Sheet35"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -4748,13 +6849,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4774,10 +6875,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4785,7 +6886,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -4796,10 +6897,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4807,10 +6908,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4818,10 +6919,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4829,10 +6930,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4840,10 +6941,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4851,10 +6952,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4862,10 +6963,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4873,10 +6974,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4884,10 +6985,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4895,10 +6996,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4906,221 +7007,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
-  <sheetPr codeName="Sheet37"/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="C9" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
-  <sheetPr codeName="Sheet38"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
         <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -5132,9 +7022,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -5152,32 +7042,32 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -5185,21 +7075,21 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -5207,10 +7097,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -5218,21 +7108,21 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>1000</v>
@@ -5240,10 +7130,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C10">
         <v>10000</v>
@@ -5251,10 +7141,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -5262,10 +7152,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>10000</v>
@@ -5285,14 +7175,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
+  <sheetPr codeName="Sheet37"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="C9" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
+  <sheetPr codeName="Sheet38"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5312,10 +7243,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5323,10 +7254,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5334,10 +7265,180 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
+      <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5353,11 +7454,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="30.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.33203125" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5379,7 +7480,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5387,10 +7488,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5398,10 +7499,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5413,10 +7514,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5438,7 +7539,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5446,10 +7547,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5457,10 +7558,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5472,10 +7573,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5497,7 +7598,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5505,10 +7606,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5516,10 +7617,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28318"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F0387-B449-4BE4-80FC-E0C69F059A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C03232-C421-4A75-A71F-811F23BCE078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="39" activeTab="39" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="39" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -53,17 +53,18 @@
     <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId38"/>
     <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId39"/>
     <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId40"/>
-    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId41"/>
-    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId42"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId43"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId44"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId45"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId46"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId47"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId48"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId49"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId50"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId51"/>
+    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId41"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId42"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId43"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId44"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId45"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId46"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId47"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId48"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId49"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId50"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId51"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId52"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -86,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -652,9 +653,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -692,7 +693,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -798,7 +799,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -940,7 +941,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -950,10 +951,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BD69C2-DB57-4C60-8DCC-FB9C43CEE49A}">
   <sheetPr codeName="Sheet39"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1014,10 +1015,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C8260A-2B08-45B2-91C9-3D139644FA31}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1078,9 +1079,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801045D0-434D-4772-B50B-BAD32ADFCC6D}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
@@ -1138,10 +1139,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{312DC3EE-E575-46F9-A9B5-EB471905BC17}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1198,10 +1199,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{628A250B-2421-4501-B6A1-3551362D1E63}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
-    <col min="3" max="3" width="46.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.33203125" customWidth="1"/>
+    <col min="3" max="3" width="46.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1257,9 +1258,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67385A93-9DB4-418E-B977-B594C234D617}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1317,10 +1318,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F7954A-D9CB-47FE-8043-C26DF94F149F}">
   <sheetPr codeName="Sheet14"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1375,10 +1376,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB0B370-5042-41B9-A8EC-24D7CD1FD99D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="59.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1434,10 +1435,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81AF588-AABE-4434-A649-BE45CA5F0598}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1495,10 +1496,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5A36B1-BCE1-494C-9FF2-9E81EB69D145}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1556,11 +1557,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513E26F-ED03-4E26-8F3C-BE6B3D3F87CC}">
   <sheetPr codeName="Sheet17"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1674,11 +1675,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABAA4BE-5C71-4904-8238-AC9EDD6FB8A9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1734,9 +1735,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5419849D-2139-4751-9485-A00468AD6907}">
   <sheetPr codeName="Sheet18"/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -1902,9 +1903,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF67A45-0B54-4944-9B39-F82B26EF60B6}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -2017,10 +2018,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F105F821-5E53-4FD8-9F07-CF97205700C1}">
   <sheetPr codeName="Sheet20"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2165,10 +2166,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC101BFC-1550-4137-B012-E4749B310065}">
   <sheetPr codeName="Sheet21"/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2301,11 +2302,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1896B5C7-9641-468E-8213-95D0BE0FBE7C}">
   <sheetPr codeName="Sheet22"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2350,10 +2351,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874FC87A-AF8F-49C8-9F12-715C978F4406}">
   <sheetPr codeName="Sheet23"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2432,11 +2433,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5689EA4D-03A7-4B71-84BE-6001E09A3DD3}">
   <sheetPr codeName="Sheet24"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2602,10 +2603,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366DB7B4-C63A-47E9-A3AB-3A17CFD5CE09}">
   <sheetPr codeName="Sheet25"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2771,10 +2772,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA6F82E-C68B-45AF-AB19-9A11877150E6}">
   <sheetPr codeName="Sheet26"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2941,11 +2942,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8CA48C-2A2F-44CF-A1AF-B3B67AA99C99}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3112,11 +3113,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2A7B2-CA79-4318-86DD-0D44A813A1C3}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3177,9 +3178,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B029D8-A57A-4DED-8831-111F395CEFC2}">
   <sheetPr codeName="Sheet28"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3346,10 +3347,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74E35D3-1628-483E-8955-C1943DBA1691}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3515,9 +3516,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A5EA066-8BD7-4F60-A549-8DF4B566C85E}">
   <sheetPr codeName="Sheet29"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3684,9 +3685,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EBF6E6-8687-4CE1-8BB6-330DEC350611}">
   <sheetPr codeName="Sheet30"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3853,9 +3854,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B71B207-7F71-4F84-BC32-C3056B8DABA1}">
   <sheetPr codeName="Sheet31"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4021,10 +4022,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D5F1C4-68E1-4C20-A92E-5B34A98159BC}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4135,10 +4136,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4248,11 +4249,11 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4351,10 +4352,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4409,11 +4410,11 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4811,9 +4812,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DDFB63-7F7A-4DD0-8939-BEB21ABE0A0F}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4980,10 +4981,10 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5366,12 +5367,13 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A3D5E-28AB-4508-8B8B-48E70AEB7A6C}">
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="38.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5392,8 +5394,8 @@
       <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>9</v>
+      <c r="C2" s="11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5434,10 +5436,10 @@
         <v>29</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6">
-        <v>90</v>
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5445,10 +5447,10 @@
         <v>29</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5456,10 +5458,10 @@
         <v>29</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8">
-        <v>50</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -5467,9 +5469,9 @@
         <v>29</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9">
+        <v>87</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5478,10 +5480,10 @@
         <v>29</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5489,10 +5491,10 @@
         <v>29</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
+        <v>107</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5500,10 +5502,10 @@
         <v>29</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>108</v>
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -5511,10 +5513,10 @@
         <v>29</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
+        <v>109</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -5522,10 +5524,10 @@
         <v>29</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -5533,10 +5535,10 @@
         <v>29</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
+        <v>112</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -5544,10 +5546,10 @@
         <v>29</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
+        <v>113</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5555,18 +5557,18 @@
         <v>29</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>114</v>
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -5577,10 +5579,10 @@
         <v>115</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5588,7 +5590,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
         <v>86</v>
@@ -5599,10 +5601,10 @@
         <v>115</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -5610,10 +5612,10 @@
         <v>115</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -5621,10 +5623,10 @@
         <v>115</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -5632,10 +5634,10 @@
         <v>115</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -5643,10 +5645,10 @@
         <v>115</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -5654,10 +5656,10 @@
         <v>115</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5665,10 +5667,10 @@
         <v>115</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -5676,10 +5678,10 @@
         <v>115</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -5687,10 +5689,10 @@
         <v>115</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -5698,7 +5700,7 @@
         <v>115</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -5709,10 +5711,10 @@
         <v>115</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -5720,7 +5722,7 @@
         <v>115</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
         <v>86</v>
@@ -5731,7 +5733,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s">
         <v>86</v>
@@ -5742,20 +5744,9 @@
         <v>115</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C35" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5765,12 +5756,12 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5877,10 +5868,10 @@
         <v>29</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
+        <v>87</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5888,10 +5879,10 @@
         <v>29</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
+        <v>106</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -5899,18 +5890,18 @@
         <v>29</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
+        <v>107</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -5918,54 +5909,54 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
+        <v>109</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
+        <v>112</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" t="s">
-        <v>86</v>
+        <v>113</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -5976,10 +5967,10 @@
         <v>115</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -5987,10 +5978,10 @@
         <v>115</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -5998,7 +5989,7 @@
         <v>115</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
         <v>86</v>
@@ -6009,10 +6000,10 @@
         <v>115</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6020,10 +6011,10 @@
         <v>115</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6031,7 +6022,7 @@
         <v>115</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -6042,10 +6033,10 @@
         <v>115</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6053,10 +6044,10 @@
         <v>115</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6064,7 +6055,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
         <v>86</v>
@@ -6075,10 +6066,10 @@
         <v>115</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6086,9 +6077,75 @@
         <v>115</v>
       </c>
       <c r="B29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C35" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6098,12 +6155,12 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6119,65 +6176,65 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -6185,32 +6242,32 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -6218,10 +6275,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -6229,10 +6286,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -6240,13 +6297,189 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>28</v>
+        <v>115</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -6255,13 +6488,170 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6424,15 +6814,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6594,13 +6984,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6763,13 +7153,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6800,14 +7190,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6846,175 +7236,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
-  <sheetPr codeName="Sheet36"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
-  <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -7022,9 +7243,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE106B-11CB-4012-8BB8-CD21B4581FD8}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -7176,12 +7397,181 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
+  <sheetPr codeName="Sheet36"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
@@ -7216,14 +7606,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7390,10 +7780,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE354EA7-EF61-4CF6-8FD9-4C0F8CF01A30}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7454,11 +7844,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC5EB7D-13BF-4B5E-895C-F5B651828B55}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="62.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7514,10 +7904,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C170638-B62F-4953-B95A-AF6F648592AA}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7573,10 +7963,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E9C587-3A78-4B4A-BCAE-07DA844DEBEA}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D6B171-50EA-4E75-9C9D-71075E3ECE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FC88FD-5E9E-464C-9AEA-CF8D4CF2889E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="39" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="35" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -48,24 +48,25 @@
     <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId33"/>
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
     <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
-    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId36"/>
-    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId37"/>
-    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId38"/>
-    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId39"/>
-    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId40"/>
-    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId41"/>
-    <sheet name="Sheet2" sheetId="58" r:id="rId42"/>
-    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId43"/>
-    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId44"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId45"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId46"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId47"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId48"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId49"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId50"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId51"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId52"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId53"/>
+    <sheet name="Grantee_Leads_CAS-HHS0001212745" sheetId="59" r:id="rId36"/>
+    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId37"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId38"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId39"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId40"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId41"/>
+    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId42"/>
+    <sheet name="Sheet2" sheetId="58" r:id="rId43"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId44"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId45"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId46"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId47"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId48"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId49"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId50"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId51"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId52"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId53"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId54"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="143">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -514,6 +515,9 @@
   </si>
   <si>
     <t>RichTextArea1__c</t>
+  </si>
+  <si>
+    <t>CAS-HHS0001212745</t>
   </si>
 </sst>
 </file>
@@ -4135,6 +4139,119 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2441CEEE-9CD5-4C8F-8478-53A90F75A93B}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4247,7 +4364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4350,7 +4467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4405,407 +4522,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>122</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>122</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4980,6 +4696,407 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5367,7 +5484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE27BAAE-CFD6-49EB-92C1-4C1E4D395BD6}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5756,7 +5873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2A0686-D278-4AC7-8259-F9DC9C794771}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5765,7 +5882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6164,7 +6281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6497,7 +6614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6654,7 +6771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
@@ -6824,7 +6941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
@@ -6994,7 +7111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
@@ -7156,43 +7273,6 @@
       </c>
       <c r="C14" s="7" t="s">
         <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7358,6 +7438,43 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -7406,7 +7523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -7575,7 +7692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
@@ -7616,7 +7733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D6B171-50EA-4E75-9C9D-71075E3ECE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188F8C8F-0A23-46BB-9E9E-D2771A192571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="39" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="34" activeTab="35" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -48,24 +48,25 @@
     <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId33"/>
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
     <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
-    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId36"/>
-    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId37"/>
-    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId38"/>
-    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId39"/>
-    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId40"/>
-    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId41"/>
-    <sheet name="Sheet2" sheetId="58" r:id="rId42"/>
-    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId43"/>
-    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId44"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId45"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId46"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId47"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId48"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId49"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId50"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId51"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId52"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId53"/>
+    <sheet name="Grantee_Leads_CAS-HHS0001212745" sheetId="59" r:id="rId36"/>
+    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId37"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId38"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId39"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId40"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId41"/>
+    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId42"/>
+    <sheet name="Sheet2" sheetId="58" r:id="rId43"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId44"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId45"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId46"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId47"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId48"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId49"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId50"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId51"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId52"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId53"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId54"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="143">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -514,6 +515,9 @@
   </si>
   <si>
     <t>RichTextArea1__c</t>
+  </si>
+  <si>
+    <t>CAS-HHS0001241410</t>
   </si>
 </sst>
 </file>
@@ -4135,6 +4139,119 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD74E99E-C8EB-45DB-8AC2-ADFE8808E3CC}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="53" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4247,7 +4364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4350,7 +4467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4405,407 +4522,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>122</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>122</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4980,6 +4696,407 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5367,7 +5484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE27BAAE-CFD6-49EB-92C1-4C1E4D395BD6}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5756,7 +5873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2A0686-D278-4AC7-8259-F9DC9C794771}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5765,7 +5882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6164,7 +6281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6497,7 +6614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6654,7 +6771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
@@ -6824,7 +6941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
@@ -6994,7 +7111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:C14"/>
@@ -7156,43 +7273,6 @@
       </c>
       <c r="C14" s="7" t="s">
         <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7358,6 +7438,43 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -7406,7 +7523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -7575,7 +7692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
@@ -7616,7 +7733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FC88FD-5E9E-464C-9AEA-CF8D4CF2889E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AB9964-C6D4-4DF9-B4C0-4C7296BC0A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="35" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="36" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -49,24 +49,25 @@
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
     <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
     <sheet name="Grantee_Leads_CAS-HHS0001212745" sheetId="59" r:id="rId36"/>
-    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId37"/>
-    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId38"/>
-    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId39"/>
-    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId40"/>
-    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId41"/>
-    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId42"/>
-    <sheet name="Sheet2" sheetId="58" r:id="rId43"/>
-    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId44"/>
-    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId45"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId46"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId47"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId48"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId49"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId50"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId51"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId52"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId53"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId54"/>
+    <sheet name="Grantee_Leads_CAS-HHS0001212704" sheetId="60" r:id="rId37"/>
+    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId38"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId39"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId40"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId41"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId42"/>
+    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId43"/>
+    <sheet name="Sheet2" sheetId="58" r:id="rId44"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId45"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId46"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId47"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId48"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId49"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId50"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId51"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId52"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId53"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId54"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId55"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="144">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -518,6 +519,9 @@
   </si>
   <si>
     <t>CAS-HHS0001212745</t>
+  </si>
+  <si>
+    <t>CAS-HHS0001212704</t>
   </si>
 </sst>
 </file>
@@ -4252,6 +4256,119 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC020E3F-9A4F-4380-8601-0ACA44065B96}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4364,7 +4481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4460,64 +4577,6 @@
       </c>
       <c r="C8">
         <v>10000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4696,6 +4755,64 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5096,7 +5213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5484,7 +5601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE27BAAE-CFD6-49EB-92C1-4C1E4D395BD6}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5873,7 +5990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2A0686-D278-4AC7-8259-F9DC9C794771}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5882,7 +5999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6281,7 +6398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6614,7 +6731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6771,7 +6888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
@@ -6941,7 +7058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
@@ -7093,175 +7210,6 @@
       </c>
       <c r="C13" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
-  <sheetPr codeName="Sheet34"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -7438,6 +7386,175 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
+  <sheetPr codeName="Sheet34"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -7474,7 +7591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -7523,7 +7640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -7692,7 +7809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
@@ -7733,7 +7850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D6B171-50EA-4E75-9C9D-71075E3ECE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05AB9964-C6D4-4DF9-B4C0-4C7296BC0A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="39" activeTab="40" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="795" firstSheet="33" activeTab="36" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -48,24 +48,26 @@
     <sheet name="Creation Second Modal FA" sheetId="24" r:id="rId33"/>
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
     <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
-    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId36"/>
-    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId37"/>
-    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId38"/>
-    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId39"/>
-    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId40"/>
-    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId41"/>
-    <sheet name="Sheet2" sheetId="58" r:id="rId42"/>
-    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId43"/>
-    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId44"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId45"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId46"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId47"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId48"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId49"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId50"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId51"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId52"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId53"/>
+    <sheet name="Grantee_Leads_CAS-HHS0001212745" sheetId="59" r:id="rId36"/>
+    <sheet name="Grantee_Leads_CAS-HHS0001212704" sheetId="60" r:id="rId37"/>
+    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId38"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId39"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId40"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId41"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId42"/>
+    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId43"/>
+    <sheet name="Sheet2" sheetId="58" r:id="rId44"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId45"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId46"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId47"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId48"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId49"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId50"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId51"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId52"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId53"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId54"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId55"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="144">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -514,6 +516,12 @@
   </si>
   <si>
     <t>RichTextArea1__c</t>
+  </si>
+  <si>
+    <t>CAS-HHS0001212745</t>
+  </si>
+  <si>
+    <t>CAS-HHS0001212704</t>
   </si>
 </sst>
 </file>
@@ -4135,6 +4143,232 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2441CEEE-9CD5-4C8F-8478-53A90F75A93B}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC020E3F-9A4F-4380-8601-0ACA44065B96}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4247,7 +4481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4347,465 +4581,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
-  <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>122</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>122</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>122</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C33" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4980,6 +4755,465 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FD23B6-DB16-49EB-89A8-BE20588C8004}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD489B9-7D28-4D0A-968C-65911560FD33}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5367,7 +5601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE27BAAE-CFD6-49EB-92C1-4C1E4D395BD6}">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5756,7 +5990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E2A0686-D278-4AC7-8259-F9DC9C794771}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -5765,7 +5999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8878618-1E7E-452C-8F3E-1824580DC013}">
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6164,7 +6398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322F882-9846-42CB-AFD8-EF8376DE9FFF}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6497,7 +6731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABB0E19-6DD3-4701-AD61-80C76D45A082}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6654,7 +6888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFE25EE6-66F5-4951-9D0C-F6559D035D9C}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:C14"/>
@@ -6824,7 +7058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83C7FC7-2A18-436E-A373-D289D769241C}">
   <sheetPr codeName="Sheet33"/>
   <dimension ref="A1:C14"/>
@@ -6987,212 +7221,6 @@
       </c>
       <c r="C14" s="7" t="s">
         <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
-  <sheetPr codeName="Sheet34"/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7358,6 +7386,212 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A3BD1-3EAB-4C67-9345-90730B6A7403}">
+  <sheetPr codeName="Sheet34"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B540E81-1FD2-4AA2-8DEE-8BFB8B274149}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A836B93B-2094-42BE-9D92-A2EB5434CB28}">
   <sheetPr codeName="Sheet35"/>
   <dimension ref="A1:C3"/>
@@ -7406,7 +7640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB402F88-9436-4279-8D3B-028474BBC575}">
   <sheetPr codeName="Sheet36"/>
   <dimension ref="A1:C14"/>
@@ -7575,7 +7809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C91C76-2A92-4FAB-8589-A8F89F7DC3A0}">
   <sheetPr codeName="Sheet37"/>
   <dimension ref="A1:C9"/>
@@ -7616,7 +7850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72FB96-7C2F-4711-BDC9-46D87BC44E74}">
   <sheetPr codeName="Sheet38"/>
   <dimension ref="A1:C14"/>

--- a/src/main/resources/Announcement_Field_Values.xlsx
+++ b/src/main/resources/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188F8C8F-0A23-46BB-9E9E-D2771A192571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0FF639-FE36-46CC-BF07-4EEE7FDD8E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="34" activeTab="35" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="795" firstSheet="34" activeTab="36" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
@@ -49,24 +49,25 @@
     <sheet name="Creation Second Modal1" sheetId="14" r:id="rId34"/>
     <sheet name="Grantee_Leads_Creation" sheetId="49" r:id="rId35"/>
     <sheet name="Grantee_Leads_CAS-HHS0001212745" sheetId="59" r:id="rId36"/>
-    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId37"/>
-    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId38"/>
-    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId39"/>
-    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId40"/>
-    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId41"/>
-    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId42"/>
-    <sheet name="Sheet2" sheetId="58" r:id="rId43"/>
-    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId44"/>
-    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId45"/>
-    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId46"/>
-    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId47"/>
-    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId48"/>
-    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId49"/>
-    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId50"/>
-    <sheet name="EnterReview" sheetId="9" r:id="rId51"/>
-    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId52"/>
-    <sheet name="Edition2" sheetId="12" r:id="rId53"/>
-    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId54"/>
+    <sheet name="Grantee_Leads_CAS-HHS0001222659" sheetId="60" r:id="rId37"/>
+    <sheet name="Grantee_Leads_Creation_Cost_No" sheetId="56" r:id="rId38"/>
+    <sheet name="Grantee_Leads_Edition" sheetId="50" r:id="rId39"/>
+    <sheet name="Grantee_Qualifiedleads_Edition" sheetId="51" r:id="rId40"/>
+    <sheet name="Grantee_Opportunity_Edition" sheetId="52" r:id="rId41"/>
+    <sheet name="Grantee_Opp_PreAppNo_Edition" sheetId="53" r:id="rId42"/>
+    <sheet name="Grantee_Opp_PreAppYes_Edition" sheetId="57" r:id="rId43"/>
+    <sheet name="Sheet2" sheetId="58" r:id="rId44"/>
+    <sheet name="Grantee_Opp_PreApp_NonContruct" sheetId="54" r:id="rId45"/>
+    <sheet name="GranteePreAppNonContructSettNo" sheetId="55" r:id="rId46"/>
+    <sheet name="Creation Second Modal Undo" sheetId="47" r:id="rId47"/>
+    <sheet name="Creation Second Modal3" sheetId="17" r:id="rId48"/>
+    <sheet name="Creation Second Modal4" sheetId="18" r:id="rId49"/>
+    <sheet name="Creation of pre-app_nego_yes" sheetId="15" r:id="rId50"/>
+    <sheet name="budget_Details_Subaward_Yes" sheetId="45" r:id="rId51"/>
+    <sheet name="EnterReview" sheetId="9" r:id="rId52"/>
+    <sheet name="Pre-Application Modal" sheetId="11" r:id="rId53"/>
+    <sheet name="Edition2" sheetId="12" r:id="rId54"/>
+    <sheet name="RiskAssessmentNo" sheetId="13" r:id="rId55"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="143">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4252,6 +4253,115 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89ED4B1E-5C2A-42D8-8A86-C2A9E63B9266}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65CC1C52-FEAB-4BC2-90D1-ACBAA592B349}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4364,7 +4474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A61549-7A09-42D8-B378-89BCE97801B7}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -4460,64 +4570,6 @@
       </c>
       <c r="C8">
         <v>10000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E30494C-3CF8-41CD-A871-52E96E60A3C8}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4696,6 +4748,64 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://sche